--- a/data/archive/2026-08-10-main-ledger-archived-shadow-primary/tennis.xlsx
+++ b/data/archive/2026-08-10-main-ledger-archived-shadow-primary/tennis.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Picks" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Picks" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Summary'!$A$1:$L$19</definedName>
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS21" headerRowCount="1">
-  <autoFilter ref="A1:CS21"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS38" headerRowCount="1">
+  <autoFilter ref="A1:CS38"/>
   <tableColumns count="97">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -756,19 +756,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$21)</f>
+        <f>COUNTA('Picks'!$A$2:$A$38)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$21,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$38,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$21,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$38,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"win")+COUNTIFS('Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$38,"settled",'Picks'!$V$2:$V$38,"win")+COUNTIFS('Picks'!$U$2:$U$38,"settled",'Picks'!$V$2:$V$38,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -796,19 +796,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$21,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$38,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$21,"&gt;0",'Picks'!$V$2:$V$21,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$21,"&gt;0",'Picks'!$V$2:$V$21,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$38,"&gt;0",'Picks'!$V$2:$V$38,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$38,"&gt;0",'Picks'!$V$2:$V$38,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$21,"&gt;0",'Picks'!$V$2:$V$21,"win")/(COUNTIFS('Picks'!$BX$2:$BX$21,"&gt;0",'Picks'!$V$2:$V$21,"win")+COUNTIFS('Picks'!$BX$2:$BX$21,"&gt;0",'Picks'!$V$2:$V$21,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$38,"&gt;0",'Picks'!$V$2:$V$38,"win")/(COUNTIFS('Picks'!$BX$2:$BX$38,"&gt;0",'Picks'!$V$2:$V$38,"win")+COUNTIFS('Picks'!$BX$2:$BX$38,"&gt;0",'Picks'!$V$2:$V$38,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$21)/SUM('Picks'!$BX$2:$BX$21),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$38)/SUM('Picks'!$BX$2:$BX$38),0)</f>
         <v/>
       </c>
     </row>
@@ -836,19 +836,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$21)</f>
+        <f>SUM('Picks'!$BY$2:$BY$38)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$21,"&lt;&gt;",'Picks'!$AB$2:$AB$21),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$38,"&lt;&gt;",'Picks'!$AB$2:$AB$38),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$21,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$21,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$38,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$38,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$21,'Picks'!$AM$2:$AM$21,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$38,'Picks'!$AM$2:$AM$38,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -903,15 +903,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$21,$A14,'Picks'!$U$2:$U$21,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$38,$A14,'Picks'!$U$2:$U$38,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$21,$A14,'Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$38,$A14,'Picks'!$U$2:$U$38,"settled",'Picks'!$V$2:$V$38,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$21,$A14,'Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$38,$A14,'Picks'!$U$2:$U$38,"settled",'Picks'!$V$2:$V$38,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -919,11 +919,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$21,'Picks'!$H$2:$H$21,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$38,'Picks'!$H$2:$H$38,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$21,'Picks'!$H$2:$H$21,$A14,'Picks'!$U$2:$U$21,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$38,'Picks'!$H$2:$H$38,$A14,'Picks'!$U$2:$U$38,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -934,15 +934,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$21,$A15,'Picks'!$U$2:$U$21,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$38,$A15,'Picks'!$U$2:$U$38,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$21,$A15,'Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$38,$A15,'Picks'!$U$2:$U$38,"settled",'Picks'!$V$2:$V$38,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$21,$A15,'Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$38,$A15,'Picks'!$U$2:$U$38,"settled",'Picks'!$V$2:$V$38,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -950,11 +950,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$21,'Picks'!$H$2:$H$21,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$38,'Picks'!$H$2:$H$38,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$21,'Picks'!$H$2:$H$21,$A15,'Picks'!$U$2:$U$21,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$38,'Picks'!$H$2:$H$38,$A15,'Picks'!$U$2:$U$38,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -965,15 +965,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$21,$A16,'Picks'!$U$2:$U$21,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$38,$A16,'Picks'!$U$2:$U$38,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$21,$A16,'Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$38,$A16,'Picks'!$U$2:$U$38,"settled",'Picks'!$V$2:$V$38,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$21,$A16,'Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$38,$A16,'Picks'!$U$2:$U$38,"settled",'Picks'!$V$2:$V$38,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -981,11 +981,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$21,'Picks'!$H$2:$H$21,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$38,'Picks'!$H$2:$H$38,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$21,'Picks'!$H$2:$H$21,$A16,'Picks'!$U$2:$U$21,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$38,'Picks'!$H$2:$H$38,$A16,'Picks'!$U$2:$U$38,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CS21"/>
+  <dimension ref="A1:CS38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4636,18 +4636,38 @@
       </c>
       <c r="U12" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V12" s="24" t="n"/>
-      <c r="W12" s="26" t="n"/>
-      <c r="X12" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V12" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W12" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y12" s="25" t="n"/>
-      <c r="Z12" s="26" t="n"/>
-      <c r="AA12" s="28" t="n"/>
-      <c r="AB12" s="28" t="n"/>
-      <c r="AC12" s="30" t="n"/>
-      <c r="AD12" s="24" t="n"/>
+      <c r="Z12" s="26" t="n">
+        <v>150</v>
+      </c>
+      <c r="AA12" s="28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AB12" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD12" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T21:58:39.165848Z</t>
+        </is>
+      </c>
       <c r="AE12" s="31" t="inlineStr">
         <is>
           <t>Surface-blended Elo on Hard: Adrian Mannarino p=0.565 vs Jacob Fearnley. Executable ask 0.4000 (aec-atp-jacfea-adrman-2026-08-03).</t>
@@ -4660,7 +4680,7 @@
       </c>
       <c r="AG12" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH12" s="24" t="n"/>
@@ -4790,8 +4810,12 @@
       <c r="BN12" s="28" t="n"/>
       <c r="BO12" s="28" t="n"/>
       <c r="BP12" s="25" t="n"/>
-      <c r="BQ12" s="27" t="n"/>
-      <c r="BR12" s="28" t="n"/>
+      <c r="BQ12" s="27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BR12" s="28" t="n">
+        <v>0.4</v>
+      </c>
       <c r="BS12" s="28" t="n"/>
       <c r="BT12" s="28" t="n"/>
       <c r="BU12" s="25" t="n"/>
@@ -6007,22 +6031,22 @@
     <row r="17" ht="36" customHeight="1">
       <c r="A17" s="24" t="inlineStr">
         <is>
-          <t>8df4f78345b2416b</t>
+          <t>15d8ba8c18cb4af9</t>
         </is>
       </c>
       <c r="B17" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:17.456036Z</t>
+          <t>2026-08-04T15:02:48.664333Z</t>
         </is>
       </c>
       <c r="C17" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T18:00Z</t>
+          <t>2026-08-04T16:30Z</t>
         </is>
       </c>
       <c r="D17" s="24" t="inlineStr">
         <is>
-          <t>421-2026:182202</t>
+          <t>421-2026:181813</t>
         </is>
       </c>
       <c r="E17" s="24" t="inlineStr">
@@ -6032,12 +6056,12 @@
       </c>
       <c r="F17" s="24" t="inlineStr">
         <is>
-          <t>Talia Gibson</t>
+          <t>Liam Draxl</t>
         </is>
       </c>
       <c r="G17" s="24" t="inlineStr">
         <is>
-          <t>Maja Chwalinska</t>
+          <t>Daniel Merida</t>
         </is>
       </c>
       <c r="H17" s="24" t="inlineStr">
@@ -6057,28 +6081,28 @@
         </is>
       </c>
       <c r="L17" s="26" t="n">
-        <v>117</v>
+        <v>-144</v>
       </c>
       <c r="M17" s="27" t="n">
-        <v>2.17</v>
+        <v>1.694444</v>
       </c>
       <c r="N17" s="28" t="n">
-        <v>0.460829</v>
+        <v>0.590164</v>
       </c>
       <c r="O17" s="28" t="n">
-        <v>0.623502</v>
+        <v>0.69073</v>
       </c>
       <c r="P17" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q17" s="28" t="n">
-        <v>0.162673</v>
+        <v>0.100566</v>
       </c>
       <c r="R17" s="26" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="S17" s="29" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="T17" s="24" t="inlineStr">
         <is>
@@ -6087,21 +6111,41 @@
       </c>
       <c r="U17" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V17" s="24" t="n"/>
-      <c r="W17" s="26" t="n"/>
-      <c r="X17" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V17" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W17" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y17" s="25" t="n"/>
-      <c r="Z17" s="26" t="n"/>
-      <c r="AA17" s="28" t="n"/>
-      <c r="AB17" s="28" t="n"/>
-      <c r="AC17" s="30" t="n"/>
-      <c r="AD17" s="24" t="n"/>
+      <c r="Z17" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="AA17" s="28" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="AB17" s="28" t="n">
+        <v>-0.000164</v>
+      </c>
+      <c r="AC17" s="30" t="n">
+        <v>1.3889</v>
+      </c>
+      <c r="AD17" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T21:58:40.052341Z</t>
+        </is>
+      </c>
       <c r="AE17" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Talia Gibson p=0.376 vs Maja Chwalinska. Executable ask 0.4600 (aec-wta-majchw-talgib-2026-08-04).</t>
+          <t>Surface-blended Elo on Hard: Liam Draxl p=0.309 vs Daniel Merida. Executable ask 0.5900 (aec-atp-danagu-liadra-2026-08-03).</t>
         </is>
       </c>
       <c r="AF17" s="31" t="inlineStr">
@@ -6142,32 +6186,32 @@
       </c>
       <c r="AP17" s="24" t="inlineStr">
         <is>
-          <t>Talia Gibson</t>
+          <t>Liam Draxl</t>
         </is>
       </c>
       <c r="AQ17" s="24" t="inlineStr">
         <is>
-          <t>Talia Gibson</t>
+          <t>Liam Draxl</t>
         </is>
       </c>
       <c r="AR17" s="24" t="inlineStr">
         <is>
-          <t>Talia Gibson</t>
+          <t>Liam Draxl</t>
         </is>
       </c>
       <c r="AS17" s="24" t="inlineStr">
         <is>
-          <t>Maja Chwalinska</t>
+          <t>Daniel Merida</t>
         </is>
       </c>
       <c r="AT17" s="24" t="inlineStr">
         <is>
-          <t>Maja Chwalinska</t>
+          <t>Daniel Merida</t>
         </is>
       </c>
       <c r="AU17" s="24" t="inlineStr">
         <is>
-          <t>Maja Chwalinska</t>
+          <t>Daniel Merida</t>
         </is>
       </c>
       <c r="AV17" s="24" t="n"/>
@@ -6220,7 +6264,7 @@
       </c>
       <c r="BH17" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:23:27.218479Z</t>
+          <t>2026-08-04T15:01:10.821337Z</t>
         </is>
       </c>
       <c r="BI17" s="24" t="inlineStr">
@@ -6230,19 +6274,23 @@
       </c>
       <c r="BJ17" s="25" t="n"/>
       <c r="BK17" s="26" t="n">
-        <v>117</v>
+        <v>-144</v>
       </c>
       <c r="BL17" s="27" t="n">
-        <v>2.17</v>
+        <v>1.694444</v>
       </c>
       <c r="BM17" s="28" t="n">
-        <v>0.460829</v>
+        <v>0.590164</v>
       </c>
       <c r="BN17" s="28" t="n"/>
       <c r="BO17" s="28" t="n"/>
       <c r="BP17" s="25" t="n"/>
-      <c r="BQ17" s="27" t="n"/>
-      <c r="BR17" s="28" t="n"/>
+      <c r="BQ17" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="BR17" s="28" t="n">
+        <v>0.59</v>
+      </c>
       <c r="BS17" s="28" t="n"/>
       <c r="BT17" s="28" t="n"/>
       <c r="BU17" s="25" t="n"/>
@@ -6278,22 +6326,22 @@
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="24" t="inlineStr">
         <is>
-          <t>34a95956e9564070</t>
+          <t>0932626ebe0641d3</t>
         </is>
       </c>
       <c r="B18" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:17.456036Z</t>
+          <t>2026-08-04T16:52:13.548572Z</t>
         </is>
       </c>
       <c r="C18" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T16:30Z</t>
+          <t>2026-08-04T18:00Z</t>
         </is>
       </c>
       <c r="D18" s="24" t="inlineStr">
         <is>
-          <t>421-2026:181813</t>
+          <t>421-2026:182202</t>
         </is>
       </c>
       <c r="E18" s="24" t="inlineStr">
@@ -6303,12 +6351,12 @@
       </c>
       <c r="F18" s="24" t="inlineStr">
         <is>
-          <t>Liam Draxl</t>
+          <t>Talia Gibson</t>
         </is>
       </c>
       <c r="G18" s="24" t="inlineStr">
         <is>
-          <t>Daniel Merida</t>
+          <t>Maja Chwalinska</t>
         </is>
       </c>
       <c r="H18" s="24" t="inlineStr">
@@ -6328,28 +6376,28 @@
         </is>
       </c>
       <c r="L18" s="26" t="n">
-        <v>-144</v>
+        <v>122</v>
       </c>
       <c r="M18" s="27" t="n">
-        <v>1.694444</v>
+        <v>2.22</v>
       </c>
       <c r="N18" s="28" t="n">
-        <v>0.590164</v>
+        <v>0.45045</v>
       </c>
       <c r="O18" s="28" t="n">
-        <v>0.69073</v>
+        <v>0.623502</v>
       </c>
       <c r="P18" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q18" s="28" t="n">
-        <v>0.100566</v>
+        <v>0.173052</v>
       </c>
       <c r="R18" s="26" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="S18" s="29" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="T18" s="24" t="inlineStr">
         <is>
@@ -6358,21 +6406,41 @@
       </c>
       <c r="U18" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V18" s="24" t="n"/>
-      <c r="W18" s="26" t="n"/>
-      <c r="X18" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V18" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W18" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X18" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y18" s="25" t="n"/>
-      <c r="Z18" s="26" t="n"/>
-      <c r="AA18" s="28" t="n"/>
-      <c r="AB18" s="28" t="n"/>
-      <c r="AC18" s="30" t="n"/>
-      <c r="AD18" s="24" t="n"/>
+      <c r="Z18" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="AA18" s="28" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AB18" s="28" t="n">
+        <v>-0.00045</v>
+      </c>
+      <c r="AC18" s="30" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AD18" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T21:58:40.245109Z</t>
+        </is>
+      </c>
       <c r="AE18" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Liam Draxl p=0.309 vs Daniel Merida. Executable ask 0.5900 (aec-atp-danagu-liadra-2026-08-03).</t>
+          <t>Surface-blended Elo on Hard: Talia Gibson p=0.376 vs Maja Chwalinska. Executable ask 0.4500 (aec-wta-majchw-talgib-2026-08-04).</t>
         </is>
       </c>
       <c r="AF18" s="31" t="inlineStr">
@@ -6382,7 +6450,7 @@
       </c>
       <c r="AG18" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH18" s="24" t="n"/>
@@ -6413,32 +6481,32 @@
       </c>
       <c r="AP18" s="24" t="inlineStr">
         <is>
-          <t>Liam Draxl</t>
+          <t>Talia Gibson</t>
         </is>
       </c>
       <c r="AQ18" s="24" t="inlineStr">
         <is>
-          <t>Liam Draxl</t>
+          <t>Talia Gibson</t>
         </is>
       </c>
       <c r="AR18" s="24" t="inlineStr">
         <is>
-          <t>Liam Draxl</t>
+          <t>Talia Gibson</t>
         </is>
       </c>
       <c r="AS18" s="24" t="inlineStr">
         <is>
-          <t>Daniel Merida</t>
+          <t>Maja Chwalinska</t>
         </is>
       </c>
       <c r="AT18" s="24" t="inlineStr">
         <is>
-          <t>Daniel Merida</t>
+          <t>Maja Chwalinska</t>
         </is>
       </c>
       <c r="AU18" s="24" t="inlineStr">
         <is>
-          <t>Daniel Merida</t>
+          <t>Maja Chwalinska</t>
         </is>
       </c>
       <c r="AV18" s="24" t="n"/>
@@ -6491,7 +6559,7 @@
       </c>
       <c r="BH18" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:23:40.504586Z</t>
+          <t>2026-08-04T16:50:30.241150Z</t>
         </is>
       </c>
       <c r="BI18" s="24" t="inlineStr">
@@ -6501,19 +6569,23 @@
       </c>
       <c r="BJ18" s="25" t="n"/>
       <c r="BK18" s="26" t="n">
-        <v>-144</v>
+        <v>122</v>
       </c>
       <c r="BL18" s="27" t="n">
-        <v>1.694444</v>
+        <v>2.22</v>
       </c>
       <c r="BM18" s="28" t="n">
-        <v>0.590164</v>
+        <v>0.45045</v>
       </c>
       <c r="BN18" s="28" t="n"/>
       <c r="BO18" s="28" t="n"/>
       <c r="BP18" s="25" t="n"/>
-      <c r="BQ18" s="27" t="n"/>
-      <c r="BR18" s="28" t="n"/>
+      <c r="BQ18" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BR18" s="28" t="n">
+        <v>0.45</v>
+      </c>
       <c r="BS18" s="28" t="n"/>
       <c r="BT18" s="28" t="n"/>
       <c r="BU18" s="25" t="n"/>
@@ -6549,12 +6621,12 @@
     <row r="19" ht="36" customHeight="1">
       <c r="A19" s="24" t="inlineStr">
         <is>
-          <t>ca1db046253f492f</t>
+          <t>59c5fd2e82144477</t>
         </is>
       </c>
       <c r="B19" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:17.456036Z</t>
+          <t>2026-08-04T16:52:13.548572Z</t>
         </is>
       </c>
       <c r="C19" s="24" t="inlineStr">
@@ -6629,18 +6701,38 @@
       </c>
       <c r="U19" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V19" s="24" t="n"/>
-      <c r="W19" s="26" t="n"/>
-      <c r="X19" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V19" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W19" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y19" s="25" t="n"/>
-      <c r="Z19" s="26" t="n"/>
-      <c r="AA19" s="28" t="n"/>
-      <c r="AB19" s="28" t="n"/>
-      <c r="AC19" s="30" t="n"/>
-      <c r="AD19" s="24" t="n"/>
+      <c r="Z19" s="26" t="n">
+        <v>-203</v>
+      </c>
+      <c r="AA19" s="28" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AB19" s="28" t="n">
+        <v>3.3e-05</v>
+      </c>
+      <c r="AC19" s="30" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD19" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T21:58:40.439256Z</t>
+        </is>
+      </c>
       <c r="AE19" s="31" t="inlineStr">
         <is>
           <t>Surface-blended Elo on Hard: Jack Draper p=0.782 vs Terence Atmane. Executable ask 0.6700 (aec-atp-teratm-jacdra-2026-08-03).</t>
@@ -6653,7 +6745,7 @@
       </c>
       <c r="AG19" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH19" s="24" t="n"/>
@@ -6762,7 +6854,7 @@
       </c>
       <c r="BH19" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:23:45.147148Z</t>
+          <t>2026-08-04T16:50:46.373890Z</t>
         </is>
       </c>
       <c r="BI19" s="24" t="inlineStr">
@@ -6783,8 +6875,12 @@
       <c r="BN19" s="28" t="n"/>
       <c r="BO19" s="28" t="n"/>
       <c r="BP19" s="25" t="n"/>
-      <c r="BQ19" s="27" t="n"/>
-      <c r="BR19" s="28" t="n"/>
+      <c r="BQ19" s="27" t="n">
+        <v>1.492611</v>
+      </c>
+      <c r="BR19" s="28" t="n">
+        <v>0.67</v>
+      </c>
       <c r="BS19" s="28" t="n"/>
       <c r="BT19" s="28" t="n"/>
       <c r="BU19" s="25" t="n"/>
@@ -6820,22 +6916,22 @@
     <row r="20" ht="36" customHeight="1">
       <c r="A20" s="24" t="inlineStr">
         <is>
-          <t>ad8183bf5b564dee</t>
+          <t>ebdce4914c024acf</t>
         </is>
       </c>
       <c r="B20" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:17.456036Z</t>
+          <t>2026-08-05T10:21:33.669433Z</t>
         </is>
       </c>
       <c r="C20" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T23:00Z</t>
+          <t>2026-08-05T10:30Z</t>
         </is>
       </c>
       <c r="D20" s="24" t="inlineStr">
         <is>
-          <t>421-2026:181748</t>
+          <t>961-2026:182098</t>
         </is>
       </c>
       <c r="E20" s="24" t="inlineStr">
@@ -6845,12 +6941,12 @@
       </c>
       <c r="F20" s="24" t="inlineStr">
         <is>
-          <t>Marin Cilic</t>
+          <t>Mona Barthel</t>
         </is>
       </c>
       <c r="G20" s="24" t="inlineStr">
         <is>
-          <t>Frances Tiafoe</t>
+          <t>Martyna Kubka</t>
         </is>
       </c>
       <c r="H20" s="24" t="inlineStr">
@@ -6860,7 +6956,7 @@
       </c>
       <c r="I20" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J20" s="25" t="n"/>
@@ -6870,28 +6966,28 @@
         </is>
       </c>
       <c r="L20" s="26" t="n">
-        <v>-178</v>
+        <v>156</v>
       </c>
       <c r="M20" s="27" t="n">
-        <v>1.561798</v>
+        <v>2.56</v>
       </c>
       <c r="N20" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.390625</v>
       </c>
       <c r="O20" s="28" t="n">
-        <v>0.701855</v>
+        <v>0.5849800000000001</v>
       </c>
       <c r="P20" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q20" s="28" t="n">
-        <v>0.061567</v>
+        <v>0.194355</v>
       </c>
       <c r="R20" s="26" t="n">
-        <v>51</v>
+        <v>100</v>
       </c>
       <c r="S20" s="29" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="T20" s="24" t="inlineStr">
         <is>
@@ -6900,21 +6996,41 @@
       </c>
       <c r="U20" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V20" s="24" t="n"/>
-      <c r="W20" s="26" t="n"/>
-      <c r="X20" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V20" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W20" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X20" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y20" s="25" t="n"/>
-      <c r="Z20" s="26" t="n"/>
-      <c r="AA20" s="28" t="n"/>
-      <c r="AB20" s="28" t="n"/>
-      <c r="AC20" s="30" t="n"/>
-      <c r="AD20" s="24" t="n"/>
+      <c r="Z20" s="26" t="n">
+        <v>156</v>
+      </c>
+      <c r="AA20" s="28" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AB20" s="28" t="n">
+        <v>-0.000625</v>
+      </c>
+      <c r="AC20" s="30" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD20" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:49:58.226429Z</t>
+        </is>
+      </c>
       <c r="AE20" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Marin Cilic p=0.298 vs Frances Tiafoe. Executable ask 0.6400 (aec-atp-fratia-marcil-2026-08-05).</t>
+          <t>Surface-blended Elo on Hard: Mona Barthel p=0.585 vs Martyna Kubka. Executable ask 0.3900 (aec-wta-markub-monbar-2026-08-05).</t>
         </is>
       </c>
       <c r="AF20" s="31" t="inlineStr">
@@ -6955,32 +7071,32 @@
       </c>
       <c r="AP20" s="24" t="inlineStr">
         <is>
-          <t>Marin Cilic</t>
+          <t>Mona Barthel</t>
         </is>
       </c>
       <c r="AQ20" s="24" t="inlineStr">
         <is>
-          <t>Marin Cilic</t>
+          <t>Mona Barthel</t>
         </is>
       </c>
       <c r="AR20" s="24" t="inlineStr">
         <is>
-          <t>Marin Cilic</t>
+          <t>Mona Barthel</t>
         </is>
       </c>
       <c r="AS20" s="24" t="inlineStr">
         <is>
-          <t>Frances Tiafoe</t>
+          <t>Martyna Kubka</t>
         </is>
       </c>
       <c r="AT20" s="24" t="inlineStr">
         <is>
-          <t>Frances Tiafoe</t>
+          <t>Martyna Kubka</t>
         </is>
       </c>
       <c r="AU20" s="24" t="inlineStr">
         <is>
-          <t>Frances Tiafoe</t>
+          <t>Martyna Kubka</t>
         </is>
       </c>
       <c r="AV20" s="24" t="n"/>
@@ -6998,7 +7114,7 @@
       </c>
       <c r="BA20" s="24" t="inlineStr">
         <is>
-          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
         </is>
       </c>
       <c r="BB20" s="24" t="inlineStr">
@@ -7013,7 +7129,7 @@
       </c>
       <c r="BD20" s="24" t="inlineStr">
         <is>
-          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
         </is>
       </c>
       <c r="BE20" s="24" t="inlineStr">
@@ -7028,12 +7144,12 @@
       </c>
       <c r="BG20" s="24" t="inlineStr">
         <is>
-          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
         </is>
       </c>
       <c r="BH20" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:23:53.532342Z</t>
+          <t>2026-08-05T10:19:06.246493Z</t>
         </is>
       </c>
       <c r="BI20" s="24" t="inlineStr">
@@ -7043,19 +7159,23 @@
       </c>
       <c r="BJ20" s="25" t="n"/>
       <c r="BK20" s="26" t="n">
-        <v>-178</v>
+        <v>156</v>
       </c>
       <c r="BL20" s="27" t="n">
-        <v>1.561798</v>
+        <v>2.56</v>
       </c>
       <c r="BM20" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.390625</v>
       </c>
       <c r="BN20" s="28" t="n"/>
       <c r="BO20" s="28" t="n"/>
       <c r="BP20" s="25" t="n"/>
-      <c r="BQ20" s="27" t="n"/>
-      <c r="BR20" s="28" t="n"/>
+      <c r="BQ20" s="27" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BR20" s="28" t="n">
+        <v>0.39</v>
+      </c>
       <c r="BS20" s="28" t="n"/>
       <c r="BT20" s="28" t="n"/>
       <c r="BU20" s="25" t="n"/>
@@ -7091,22 +7211,22 @@
     <row r="21" ht="36" customHeight="1">
       <c r="A21" s="24" t="inlineStr">
         <is>
-          <t>e2274e5a21ab4fbc</t>
+          <t>41f6571053964a9b</t>
         </is>
       </c>
       <c r="B21" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:17.456036Z</t>
+          <t>2026-08-05T10:44:49.997481Z</t>
         </is>
       </c>
       <c r="C21" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T00:30Z</t>
+          <t>2026-08-05T12:00Z</t>
         </is>
       </c>
       <c r="D21" s="24" t="inlineStr">
         <is>
-          <t>421-2026:181769</t>
+          <t>961-2026:182097</t>
         </is>
       </c>
       <c r="E21" s="24" t="inlineStr">
@@ -7116,12 +7236,12 @@
       </c>
       <c r="F21" s="24" t="inlineStr">
         <is>
-          <t>Gabriel Diallo</t>
+          <t>Veronika Podrez</t>
         </is>
       </c>
       <c r="G21" s="24" t="inlineStr">
         <is>
-          <t>Luciano Darderi</t>
+          <t>Susan Bandecchi</t>
         </is>
       </c>
       <c r="H21" s="24" t="inlineStr">
@@ -7131,7 +7251,7 @@
       </c>
       <c r="I21" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J21" s="25" t="n"/>
@@ -7141,28 +7261,28 @@
         </is>
       </c>
       <c r="L21" s="26" t="n">
-        <v>113</v>
+        <v>-113</v>
       </c>
       <c r="M21" s="27" t="n">
-        <v>2.13</v>
+        <v>1.884956</v>
       </c>
       <c r="N21" s="28" t="n">
-        <v>0.469484</v>
+        <v>0.530516</v>
       </c>
       <c r="O21" s="28" t="n">
-        <v>0.62292</v>
+        <v>0.684504</v>
       </c>
       <c r="P21" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q21" s="28" t="n">
-        <v>0.153436</v>
+        <v>0.153988</v>
       </c>
       <c r="R21" s="26" t="n">
         <v>97</v>
       </c>
       <c r="S21" s="29" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="T21" s="24" t="inlineStr">
         <is>
@@ -7171,21 +7291,41 @@
       </c>
       <c r="U21" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V21" s="24" t="n"/>
-      <c r="W21" s="26" t="n"/>
-      <c r="X21" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V21" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W21" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y21" s="25" t="n"/>
-      <c r="Z21" s="26" t="n"/>
-      <c r="AA21" s="28" t="n"/>
-      <c r="AB21" s="28" t="n"/>
-      <c r="AC21" s="30" t="n"/>
-      <c r="AD21" s="24" t="n"/>
+      <c r="Z21" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="AA21" s="28" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AB21" s="28" t="n">
+        <v>-0.000516</v>
+      </c>
+      <c r="AC21" s="30" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD21" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T16:59:37.870671Z</t>
+        </is>
+      </c>
       <c r="AE21" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Gabriel Diallo p=0.377 vs Luciano Darderi. Executable ask 0.4700 (aec-atp-lucdar-gabdia-2026-08-05).</t>
+          <t>Surface-blended Elo on Hard: Veronika Podrez p=0.685 vs Susan Bandecchi. Executable ask 0.5300 (aec-wta-susban-verpod-2026-08-05).</t>
         </is>
       </c>
       <c r="AF21" s="31" t="inlineStr">
@@ -7195,7 +7335,7 @@
       </c>
       <c r="AG21" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH21" s="24" t="n"/>
@@ -7226,32 +7366,32 @@
       </c>
       <c r="AP21" s="24" t="inlineStr">
         <is>
-          <t>Gabriel Diallo</t>
+          <t>Veronika Podrez</t>
         </is>
       </c>
       <c r="AQ21" s="24" t="inlineStr">
         <is>
-          <t>Gabriel Diallo</t>
+          <t>Veronika Podrez</t>
         </is>
       </c>
       <c r="AR21" s="24" t="inlineStr">
         <is>
-          <t>Gabriel Diallo</t>
+          <t>Veronika Podrez</t>
         </is>
       </c>
       <c r="AS21" s="24" t="inlineStr">
         <is>
-          <t>Luciano Darderi</t>
+          <t>Susan Bandecchi</t>
         </is>
       </c>
       <c r="AT21" s="24" t="inlineStr">
         <is>
-          <t>Luciano Darderi</t>
+          <t>Susan Bandecchi</t>
         </is>
       </c>
       <c r="AU21" s="24" t="inlineStr">
         <is>
-          <t>Luciano Darderi</t>
+          <t>Susan Bandecchi</t>
         </is>
       </c>
       <c r="AV21" s="24" t="n"/>
@@ -7269,7 +7409,7 @@
       </c>
       <c r="BA21" s="24" t="inlineStr">
         <is>
-          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
         </is>
       </c>
       <c r="BB21" s="24" t="inlineStr">
@@ -7284,7 +7424,7 @@
       </c>
       <c r="BD21" s="24" t="inlineStr">
         <is>
-          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
         </is>
       </c>
       <c r="BE21" s="24" t="inlineStr">
@@ -7299,12 +7439,12 @@
       </c>
       <c r="BG21" s="24" t="inlineStr">
         <is>
-          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
         </is>
       </c>
       <c r="BH21" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:23:55.350978Z</t>
+          <t>2026-08-05T10:42:35.161195Z</t>
         </is>
       </c>
       <c r="BI21" s="24" t="inlineStr">
@@ -7314,19 +7454,23 @@
       </c>
       <c r="BJ21" s="25" t="n"/>
       <c r="BK21" s="26" t="n">
-        <v>113</v>
+        <v>-113</v>
       </c>
       <c r="BL21" s="27" t="n">
-        <v>2.13</v>
+        <v>1.884956</v>
       </c>
       <c r="BM21" s="28" t="n">
-        <v>0.469484</v>
+        <v>0.530516</v>
       </c>
       <c r="BN21" s="28" t="n"/>
       <c r="BO21" s="28" t="n"/>
       <c r="BP21" s="25" t="n"/>
-      <c r="BQ21" s="27" t="n"/>
-      <c r="BR21" s="28" t="n"/>
+      <c r="BQ21" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="BR21" s="28" t="n">
+        <v>0.53</v>
+      </c>
       <c r="BS21" s="28" t="n"/>
       <c r="BT21" s="28" t="n"/>
       <c r="BU21" s="25" t="n"/>
@@ -7359,6 +7503,4973 @@
         </is>
       </c>
     </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="24" t="inlineStr">
+        <is>
+          <t>8d670cbce19e4458</t>
+        </is>
+      </c>
+      <c r="B22" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:54:48.712587Z</t>
+        </is>
+      </c>
+      <c r="C22" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T16:30Z</t>
+        </is>
+      </c>
+      <c r="D22" s="24" t="inlineStr">
+        <is>
+          <t>421-2026:181752</t>
+        </is>
+      </c>
+      <c r="E22" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F22" s="24" t="inlineStr">
+        <is>
+          <t>Arthur Rinderknech</t>
+        </is>
+      </c>
+      <c r="G22" s="24" t="inlineStr">
+        <is>
+          <t>Miomir Kecmanovic</t>
+        </is>
+      </c>
+      <c r="H22" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I22" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J22" s="25" t="n"/>
+      <c r="K22" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L22" s="26" t="n">
+        <v>104</v>
+      </c>
+      <c r="M22" s="27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="N22" s="28" t="n">
+        <v>0.490196</v>
+      </c>
+      <c r="O22" s="28" t="n">
+        <v>0.5960220000000001</v>
+      </c>
+      <c r="P22" s="28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q22" s="28" t="n">
+        <v>0.105826</v>
+      </c>
+      <c r="R22" s="26" t="n">
+        <v>73</v>
+      </c>
+      <c r="S22" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T22" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U22" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V22" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W22" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X22" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="25" t="n"/>
+      <c r="Z22" s="26" t="n">
+        <v>104</v>
+      </c>
+      <c r="AA22" s="28" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="AB22" s="28" t="n">
+        <v>-0.000196</v>
+      </c>
+      <c r="AC22" s="30" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD22" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T20:57:58.514616Z</t>
+        </is>
+      </c>
+      <c r="AE22" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo on Hard: Arthur Rinderknech p=0.596 vs Miomir Kecmanovic. Executable ask 0.4900 (aec-atp-miokec-artrin-2026-08-05).</t>
+        </is>
+      </c>
+      <c r="AF22" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo model; singles only, WTA+ATP market coverage, not yet locked-holdout qualified -- promoted by explicit operator directive, not genuine walk-forward validation.</t>
+        </is>
+      </c>
+      <c r="AG22" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH22" s="24" t="n"/>
+      <c r="AI22" s="31" t="n"/>
+      <c r="AJ22" s="31" t="n"/>
+      <c r="AK22" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL22" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM22" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN22" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO22" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP22" s="24" t="inlineStr">
+        <is>
+          <t>Arthur Rinderknech</t>
+        </is>
+      </c>
+      <c r="AQ22" s="24" t="inlineStr">
+        <is>
+          <t>Arthur Rinderknech</t>
+        </is>
+      </c>
+      <c r="AR22" s="24" t="inlineStr">
+        <is>
+          <t>Arthur Rinderknech</t>
+        </is>
+      </c>
+      <c r="AS22" s="24" t="inlineStr">
+        <is>
+          <t>Miomir Kecmanovic</t>
+        </is>
+      </c>
+      <c r="AT22" s="24" t="inlineStr">
+        <is>
+          <t>Miomir Kecmanovic</t>
+        </is>
+      </c>
+      <c r="AU22" s="24" t="inlineStr">
+        <is>
+          <t>Miomir Kecmanovic</t>
+        </is>
+      </c>
+      <c r="AV22" s="24" t="n"/>
+      <c r="AW22" s="24" t="n"/>
+      <c r="AX22" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY22" s="24" t="n"/>
+      <c r="AZ22" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA22" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BB22" s="24" t="inlineStr">
+        <is>
+          <t>surface_blended_elo</t>
+        </is>
+      </c>
+      <c r="BC22" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD22" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BE22" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BF22" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG22" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BH22" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:52:54.747914Z</t>
+        </is>
+      </c>
+      <c r="BI22" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ22" s="25" t="n"/>
+      <c r="BK22" s="26" t="n">
+        <v>104</v>
+      </c>
+      <c r="BL22" s="27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BM22" s="28" t="n">
+        <v>0.490196</v>
+      </c>
+      <c r="BN22" s="28" t="n"/>
+      <c r="BO22" s="28" t="n"/>
+      <c r="BP22" s="25" t="n"/>
+      <c r="BQ22" s="27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BR22" s="28" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="BS22" s="28" t="n"/>
+      <c r="BT22" s="28" t="n"/>
+      <c r="BU22" s="25" t="n"/>
+      <c r="BV22" s="29" t="n"/>
+      <c r="BW22" s="24" t="n"/>
+      <c r="BX22" s="30" t="n"/>
+      <c r="BY22" s="27" t="n"/>
+      <c r="BZ22" s="24" t="n"/>
+      <c r="CA22" s="31" t="n"/>
+      <c r="CB22" s="24" t="n"/>
+      <c r="CC22" s="24" t="n"/>
+      <c r="CD22" s="24" t="n"/>
+      <c r="CE22" s="24" t="n"/>
+      <c r="CF22" s="24" t="n"/>
+      <c r="CG22" s="24" t="n"/>
+      <c r="CH22" s="24" t="n"/>
+      <c r="CI22" s="24" t="n"/>
+      <c r="CJ22" s="24" t="n"/>
+      <c r="CK22" s="24" t="n"/>
+      <c r="CL22" s="24" t="n"/>
+      <c r="CM22" s="24" t="n"/>
+      <c r="CN22" s="24" t="n"/>
+      <c r="CO22" s="24" t="n"/>
+      <c r="CP22" s="24" t="n"/>
+      <c r="CQ22" s="24" t="n"/>
+      <c r="CR22" s="24" t="n"/>
+      <c r="CS22" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="24" t="inlineStr">
+        <is>
+          <t>a8318311332241c5</t>
+        </is>
+      </c>
+      <c r="B23" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:54:48.712587Z</t>
+        </is>
+      </c>
+      <c r="C23" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T16:30Z</t>
+        </is>
+      </c>
+      <c r="D23" s="24" t="inlineStr">
+        <is>
+          <t>421-2026:181765</t>
+        </is>
+      </c>
+      <c r="E23" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F23" s="24" t="inlineStr">
+        <is>
+          <t>Ben Shelton</t>
+        </is>
+      </c>
+      <c r="G23" s="24" t="inlineStr">
+        <is>
+          <t>Jenson Brooksby</t>
+        </is>
+      </c>
+      <c r="H23" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I23" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J23" s="25" t="n"/>
+      <c r="K23" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L23" s="26" t="n">
+        <v>-300</v>
+      </c>
+      <c r="M23" s="27" t="n">
+        <v>1.333333</v>
+      </c>
+      <c r="N23" s="28" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="O23" s="28" t="n">
+        <v>0.814392</v>
+      </c>
+      <c r="P23" s="28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q23" s="28" t="n">
+        <v>0.064392</v>
+      </c>
+      <c r="R23" s="26" t="n">
+        <v>52</v>
+      </c>
+      <c r="S23" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T23" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U23" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V23" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W23" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X23" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="25" t="n"/>
+      <c r="Z23" s="26" t="n">
+        <v>-300</v>
+      </c>
+      <c r="AA23" s="28" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AB23" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" s="30" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="AD23" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T20:57:58.775278Z</t>
+        </is>
+      </c>
+      <c r="AE23" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo on Hard: Ben Shelton p=0.814 vs Jenson Brooksby. Executable ask 0.7500 (aec-atp-jenbro-benshe-2026-08-06).</t>
+        </is>
+      </c>
+      <c r="AF23" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo model; singles only, WTA+ATP market coverage, not yet locked-holdout qualified -- promoted by explicit operator directive, not genuine walk-forward validation.</t>
+        </is>
+      </c>
+      <c r="AG23" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH23" s="24" t="n"/>
+      <c r="AI23" s="31" t="n"/>
+      <c r="AJ23" s="31" t="n"/>
+      <c r="AK23" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL23" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM23" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN23" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO23" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP23" s="24" t="inlineStr">
+        <is>
+          <t>Ben Shelton</t>
+        </is>
+      </c>
+      <c r="AQ23" s="24" t="inlineStr">
+        <is>
+          <t>Ben Shelton</t>
+        </is>
+      </c>
+      <c r="AR23" s="24" t="inlineStr">
+        <is>
+          <t>Ben Shelton</t>
+        </is>
+      </c>
+      <c r="AS23" s="24" t="inlineStr">
+        <is>
+          <t>Jenson Brooksby</t>
+        </is>
+      </c>
+      <c r="AT23" s="24" t="inlineStr">
+        <is>
+          <t>Jenson Brooksby</t>
+        </is>
+      </c>
+      <c r="AU23" s="24" t="inlineStr">
+        <is>
+          <t>Jenson Brooksby</t>
+        </is>
+      </c>
+      <c r="AV23" s="24" t="n"/>
+      <c r="AW23" s="24" t="n"/>
+      <c r="AX23" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY23" s="24" t="n"/>
+      <c r="AZ23" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA23" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BB23" s="24" t="inlineStr">
+        <is>
+          <t>surface_blended_elo</t>
+        </is>
+      </c>
+      <c r="BC23" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD23" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BE23" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BF23" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG23" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BH23" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:52:57.128543Z</t>
+        </is>
+      </c>
+      <c r="BI23" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ23" s="25" t="n"/>
+      <c r="BK23" s="26" t="n">
+        <v>-300</v>
+      </c>
+      <c r="BL23" s="27" t="n">
+        <v>1.333333</v>
+      </c>
+      <c r="BM23" s="28" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BN23" s="28" t="n"/>
+      <c r="BO23" s="28" t="n"/>
+      <c r="BP23" s="25" t="n"/>
+      <c r="BQ23" s="27" t="n">
+        <v>1.333333</v>
+      </c>
+      <c r="BR23" s="28" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BS23" s="28" t="n"/>
+      <c r="BT23" s="28" t="n"/>
+      <c r="BU23" s="25" t="n"/>
+      <c r="BV23" s="29" t="n"/>
+      <c r="BW23" s="24" t="n"/>
+      <c r="BX23" s="30" t="n"/>
+      <c r="BY23" s="27" t="n"/>
+      <c r="BZ23" s="24" t="n"/>
+      <c r="CA23" s="31" t="n"/>
+      <c r="CB23" s="24" t="n"/>
+      <c r="CC23" s="24" t="n"/>
+      <c r="CD23" s="24" t="n"/>
+      <c r="CE23" s="24" t="n"/>
+      <c r="CF23" s="24" t="n"/>
+      <c r="CG23" s="24" t="n"/>
+      <c r="CH23" s="24" t="n"/>
+      <c r="CI23" s="24" t="n"/>
+      <c r="CJ23" s="24" t="n"/>
+      <c r="CK23" s="24" t="n"/>
+      <c r="CL23" s="24" t="n"/>
+      <c r="CM23" s="24" t="n"/>
+      <c r="CN23" s="24" t="n"/>
+      <c r="CO23" s="24" t="n"/>
+      <c r="CP23" s="24" t="n"/>
+      <c r="CQ23" s="24" t="n"/>
+      <c r="CR23" s="24" t="n"/>
+      <c r="CS23" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="24" t="inlineStr">
+        <is>
+          <t>90629adc75584dc7</t>
+        </is>
+      </c>
+      <c r="B24" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:03:22.897552Z</t>
+        </is>
+      </c>
+      <c r="C24" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T18:00Z</t>
+        </is>
+      </c>
+      <c r="D24" s="24" t="inlineStr">
+        <is>
+          <t>421-2026:182208</t>
+        </is>
+      </c>
+      <c r="E24" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F24" s="24" t="inlineStr">
+        <is>
+          <t>Emma Navarro</t>
+        </is>
+      </c>
+      <c r="G24" s="24" t="inlineStr">
+        <is>
+          <t>Alina Korneeva</t>
+        </is>
+      </c>
+      <c r="H24" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I24" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J24" s="25" t="n"/>
+      <c r="K24" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L24" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="M24" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="N24" s="28" t="n">
+        <v>0.530516</v>
+      </c>
+      <c r="O24" s="28" t="n">
+        <v>0.646211</v>
+      </c>
+      <c r="P24" s="28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q24" s="28" t="n">
+        <v>0.115695</v>
+      </c>
+      <c r="R24" s="26" t="n">
+        <v>78</v>
+      </c>
+      <c r="S24" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T24" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U24" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V24" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W24" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y24" s="25" t="n"/>
+      <c r="Z24" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="AA24" s="28" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AB24" s="28" t="n">
+        <v>-0.000516</v>
+      </c>
+      <c r="AC24" s="30" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="AD24" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T20:57:58.996785Z</t>
+        </is>
+      </c>
+      <c r="AE24" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo on Hard: Emma Navarro p=0.646 vs Alina Korneeva. Executable ask 0.5300 (aec-wta-alikor-emmnav-2026-08-04).</t>
+        </is>
+      </c>
+      <c r="AF24" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo model; singles only, WTA+ATP market coverage, not yet locked-holdout qualified -- promoted by explicit operator directive, not genuine walk-forward validation.</t>
+        </is>
+      </c>
+      <c r="AG24" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH24" s="24" t="n"/>
+      <c r="AI24" s="31" t="n"/>
+      <c r="AJ24" s="31" t="n"/>
+      <c r="AK24" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL24" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM24" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN24" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO24" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP24" s="24" t="inlineStr">
+        <is>
+          <t>Emma Navarro</t>
+        </is>
+      </c>
+      <c r="AQ24" s="24" t="inlineStr">
+        <is>
+          <t>Emma Navarro</t>
+        </is>
+      </c>
+      <c r="AR24" s="24" t="inlineStr">
+        <is>
+          <t>Emma Navarro</t>
+        </is>
+      </c>
+      <c r="AS24" s="24" t="inlineStr">
+        <is>
+          <t>Alina Korneeva</t>
+        </is>
+      </c>
+      <c r="AT24" s="24" t="inlineStr">
+        <is>
+          <t>Alina Korneeva</t>
+        </is>
+      </c>
+      <c r="AU24" s="24" t="inlineStr">
+        <is>
+          <t>Alina Korneeva</t>
+        </is>
+      </c>
+      <c r="AV24" s="24" t="n"/>
+      <c r="AW24" s="24" t="n"/>
+      <c r="AX24" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY24" s="24" t="n"/>
+      <c r="AZ24" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA24" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BB24" s="24" t="inlineStr">
+        <is>
+          <t>surface_blended_elo</t>
+        </is>
+      </c>
+      <c r="BC24" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD24" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BE24" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BF24" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG24" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BH24" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:01:59.688625Z</t>
+        </is>
+      </c>
+      <c r="BI24" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ24" s="25" t="n"/>
+      <c r="BK24" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="BL24" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="BM24" s="28" t="n">
+        <v>0.530516</v>
+      </c>
+      <c r="BN24" s="28" t="n"/>
+      <c r="BO24" s="28" t="n"/>
+      <c r="BP24" s="25" t="n"/>
+      <c r="BQ24" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="BR24" s="28" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="BS24" s="28" t="n"/>
+      <c r="BT24" s="28" t="n"/>
+      <c r="BU24" s="25" t="n"/>
+      <c r="BV24" s="29" t="n"/>
+      <c r="BW24" s="24" t="n"/>
+      <c r="BX24" s="30" t="n"/>
+      <c r="BY24" s="27" t="n"/>
+      <c r="BZ24" s="24" t="n"/>
+      <c r="CA24" s="31" t="n"/>
+      <c r="CB24" s="24" t="n"/>
+      <c r="CC24" s="24" t="n"/>
+      <c r="CD24" s="24" t="n"/>
+      <c r="CE24" s="24" t="n"/>
+      <c r="CF24" s="24" t="n"/>
+      <c r="CG24" s="24" t="n"/>
+      <c r="CH24" s="24" t="n"/>
+      <c r="CI24" s="24" t="n"/>
+      <c r="CJ24" s="24" t="n"/>
+      <c r="CK24" s="24" t="n"/>
+      <c r="CL24" s="24" t="n"/>
+      <c r="CM24" s="24" t="n"/>
+      <c r="CN24" s="24" t="n"/>
+      <c r="CO24" s="24" t="n"/>
+      <c r="CP24" s="24" t="n"/>
+      <c r="CQ24" s="24" t="n"/>
+      <c r="CR24" s="24" t="n"/>
+      <c r="CS24" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="24" t="inlineStr">
+        <is>
+          <t>09599bf5cbe04156</t>
+        </is>
+      </c>
+      <c r="B25" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:03:22.897552Z</t>
+        </is>
+      </c>
+      <c r="C25" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:00Z</t>
+        </is>
+      </c>
+      <c r="D25" s="24" t="inlineStr">
+        <is>
+          <t>421-2026:182214</t>
+        </is>
+      </c>
+      <c r="E25" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F25" s="24" t="inlineStr">
+        <is>
+          <t>Barbora Krejcikova</t>
+        </is>
+      </c>
+      <c r="G25" s="24" t="inlineStr">
+        <is>
+          <t>Liudmila Samsonova</t>
+        </is>
+      </c>
+      <c r="H25" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I25" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J25" s="25" t="n"/>
+      <c r="K25" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L25" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="M25" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="N25" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="O25" s="28" t="n">
+        <v>0.733479</v>
+      </c>
+      <c r="P25" s="28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q25" s="28" t="n">
+        <v>0.143315</v>
+      </c>
+      <c r="R25" s="26" t="n">
+        <v>92</v>
+      </c>
+      <c r="S25" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T25" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U25" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V25" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W25" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y25" s="25" t="n"/>
+      <c r="Z25" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="AA25" s="28" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="AB25" s="28" t="n">
+        <v>-0.000164</v>
+      </c>
+      <c r="AC25" s="30" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD25" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T00:20:17.500696Z</t>
+        </is>
+      </c>
+      <c r="AE25" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo on Hard: Barbora Krejcikova p=0.733 vs Liudmila Samsonova. Executable ask 0.5900 (aec-wta-liusam-barkre-2026-08-06).</t>
+        </is>
+      </c>
+      <c r="AF25" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo model; singles only, WTA+ATP market coverage, not yet locked-holdout qualified -- promoted by explicit operator directive, not genuine walk-forward validation.</t>
+        </is>
+      </c>
+      <c r="AG25" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH25" s="24" t="n"/>
+      <c r="AI25" s="31" t="n"/>
+      <c r="AJ25" s="31" t="n"/>
+      <c r="AK25" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL25" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM25" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN25" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO25" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP25" s="24" t="inlineStr">
+        <is>
+          <t>Barbora Krejcikova</t>
+        </is>
+      </c>
+      <c r="AQ25" s="24" t="inlineStr">
+        <is>
+          <t>Barbora Krejcikova</t>
+        </is>
+      </c>
+      <c r="AR25" s="24" t="inlineStr">
+        <is>
+          <t>Barbora Krejcikova</t>
+        </is>
+      </c>
+      <c r="AS25" s="24" t="inlineStr">
+        <is>
+          <t>Liudmila Samsonova</t>
+        </is>
+      </c>
+      <c r="AT25" s="24" t="inlineStr">
+        <is>
+          <t>Liudmila Samsonova</t>
+        </is>
+      </c>
+      <c r="AU25" s="24" t="inlineStr">
+        <is>
+          <t>Liudmila Samsonova</t>
+        </is>
+      </c>
+      <c r="AV25" s="24" t="n"/>
+      <c r="AW25" s="24" t="n"/>
+      <c r="AX25" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY25" s="24" t="n"/>
+      <c r="AZ25" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA25" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BB25" s="24" t="inlineStr">
+        <is>
+          <t>surface_blended_elo</t>
+        </is>
+      </c>
+      <c r="BC25" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD25" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BE25" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BF25" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG25" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BH25" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:02:04.621209Z</t>
+        </is>
+      </c>
+      <c r="BI25" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ25" s="25" t="n"/>
+      <c r="BK25" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="BL25" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="BM25" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="BN25" s="28" t="n"/>
+      <c r="BO25" s="28" t="n"/>
+      <c r="BP25" s="25" t="n"/>
+      <c r="BQ25" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="BR25" s="28" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="BS25" s="28" t="n"/>
+      <c r="BT25" s="28" t="n"/>
+      <c r="BU25" s="25" t="n"/>
+      <c r="BV25" s="29" t="n"/>
+      <c r="BW25" s="24" t="n"/>
+      <c r="BX25" s="30" t="n"/>
+      <c r="BY25" s="27" t="n"/>
+      <c r="BZ25" s="24" t="n"/>
+      <c r="CA25" s="31" t="n"/>
+      <c r="CB25" s="24" t="n"/>
+      <c r="CC25" s="24" t="n"/>
+      <c r="CD25" s="24" t="n"/>
+      <c r="CE25" s="24" t="n"/>
+      <c r="CF25" s="24" t="n"/>
+      <c r="CG25" s="24" t="n"/>
+      <c r="CH25" s="24" t="n"/>
+      <c r="CI25" s="24" t="n"/>
+      <c r="CJ25" s="24" t="n"/>
+      <c r="CK25" s="24" t="n"/>
+      <c r="CL25" s="24" t="n"/>
+      <c r="CM25" s="24" t="n"/>
+      <c r="CN25" s="24" t="n"/>
+      <c r="CO25" s="24" t="n"/>
+      <c r="CP25" s="24" t="n"/>
+      <c r="CQ25" s="24" t="n"/>
+      <c r="CR25" s="24" t="n"/>
+      <c r="CS25" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="36" customHeight="1">
+      <c r="A26" s="24" t="inlineStr">
+        <is>
+          <t>4eafd76864b640e2</t>
+        </is>
+      </c>
+      <c r="B26" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:03:22.897552Z</t>
+        </is>
+      </c>
+      <c r="C26" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T18:00Z</t>
+        </is>
+      </c>
+      <c r="D26" s="24" t="inlineStr">
+        <is>
+          <t>421-2026:181743</t>
+        </is>
+      </c>
+      <c r="E26" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F26" s="24" t="inlineStr">
+        <is>
+          <t>Alejandro Tabilo</t>
+        </is>
+      </c>
+      <c r="G26" s="24" t="inlineStr">
+        <is>
+          <t>Hubert Hurkacz</t>
+        </is>
+      </c>
+      <c r="H26" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I26" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J26" s="25" t="n"/>
+      <c r="K26" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L26" s="26" t="n">
+        <v>138</v>
+      </c>
+      <c r="M26" s="27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="N26" s="28" t="n">
+        <v>0.420168</v>
+      </c>
+      <c r="O26" s="28" t="n">
+        <v>0.584869</v>
+      </c>
+      <c r="P26" s="28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q26" s="28" t="n">
+        <v>0.164701</v>
+      </c>
+      <c r="R26" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S26" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T26" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U26" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V26" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W26" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y26" s="25" t="n"/>
+      <c r="Z26" s="26" t="n">
+        <v>138</v>
+      </c>
+      <c r="AA26" s="28" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AB26" s="28" t="n">
+        <v>-0.000168</v>
+      </c>
+      <c r="AC26" s="30" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AD26" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T20:57:59.221074Z</t>
+        </is>
+      </c>
+      <c r="AE26" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo on Hard: Alejandro Tabilo p=0.585 vs Hubert Hurkacz. Executable ask 0.4200 (aec-atp-hubhur-aletab-2026-08-06).</t>
+        </is>
+      </c>
+      <c r="AF26" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo model; singles only, WTA+ATP market coverage, not yet locked-holdout qualified -- promoted by explicit operator directive, not genuine walk-forward validation.</t>
+        </is>
+      </c>
+      <c r="AG26" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH26" s="24" t="n"/>
+      <c r="AI26" s="31" t="n"/>
+      <c r="AJ26" s="31" t="n"/>
+      <c r="AK26" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL26" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM26" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN26" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO26" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP26" s="24" t="inlineStr">
+        <is>
+          <t>Alejandro Tabilo</t>
+        </is>
+      </c>
+      <c r="AQ26" s="24" t="inlineStr">
+        <is>
+          <t>Alejandro Tabilo</t>
+        </is>
+      </c>
+      <c r="AR26" s="24" t="inlineStr">
+        <is>
+          <t>Alejandro Tabilo</t>
+        </is>
+      </c>
+      <c r="AS26" s="24" t="inlineStr">
+        <is>
+          <t>Hubert Hurkacz</t>
+        </is>
+      </c>
+      <c r="AT26" s="24" t="inlineStr">
+        <is>
+          <t>Hubert Hurkacz</t>
+        </is>
+      </c>
+      <c r="AU26" s="24" t="inlineStr">
+        <is>
+          <t>Hubert Hurkacz</t>
+        </is>
+      </c>
+      <c r="AV26" s="24" t="n"/>
+      <c r="AW26" s="24" t="n"/>
+      <c r="AX26" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY26" s="24" t="n"/>
+      <c r="AZ26" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA26" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BB26" s="24" t="inlineStr">
+        <is>
+          <t>surface_blended_elo</t>
+        </is>
+      </c>
+      <c r="BC26" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD26" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BE26" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BF26" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG26" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BH26" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:02:15.869129Z</t>
+        </is>
+      </c>
+      <c r="BI26" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ26" s="25" t="n"/>
+      <c r="BK26" s="26" t="n">
+        <v>138</v>
+      </c>
+      <c r="BL26" s="27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BM26" s="28" t="n">
+        <v>0.420168</v>
+      </c>
+      <c r="BN26" s="28" t="n"/>
+      <c r="BO26" s="28" t="n"/>
+      <c r="BP26" s="25" t="n"/>
+      <c r="BQ26" s="27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BR26" s="28" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="BS26" s="28" t="n"/>
+      <c r="BT26" s="28" t="n"/>
+      <c r="BU26" s="25" t="n"/>
+      <c r="BV26" s="29" t="n"/>
+      <c r="BW26" s="24" t="n"/>
+      <c r="BX26" s="30" t="n"/>
+      <c r="BY26" s="27" t="n"/>
+      <c r="BZ26" s="24" t="n"/>
+      <c r="CA26" s="31" t="n"/>
+      <c r="CB26" s="24" t="n"/>
+      <c r="CC26" s="24" t="n"/>
+      <c r="CD26" s="24" t="n"/>
+      <c r="CE26" s="24" t="n"/>
+      <c r="CF26" s="24" t="n"/>
+      <c r="CG26" s="24" t="n"/>
+      <c r="CH26" s="24" t="n"/>
+      <c r="CI26" s="24" t="n"/>
+      <c r="CJ26" s="24" t="n"/>
+      <c r="CK26" s="24" t="n"/>
+      <c r="CL26" s="24" t="n"/>
+      <c r="CM26" s="24" t="n"/>
+      <c r="CN26" s="24" t="n"/>
+      <c r="CO26" s="24" t="n"/>
+      <c r="CP26" s="24" t="n"/>
+      <c r="CQ26" s="24" t="n"/>
+      <c r="CR26" s="24" t="n"/>
+      <c r="CS26" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="24" t="inlineStr">
+        <is>
+          <t>a32e4b4ca87943a1</t>
+        </is>
+      </c>
+      <c r="B27" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:03:22.897552Z</t>
+        </is>
+      </c>
+      <c r="C27" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T19:30Z</t>
+        </is>
+      </c>
+      <c r="D27" s="24" t="inlineStr">
+        <is>
+          <t>421-2026:181753</t>
+        </is>
+      </c>
+      <c r="E27" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F27" s="24" t="inlineStr">
+        <is>
+          <t>Francisco Cerundolo</t>
+        </is>
+      </c>
+      <c r="G27" s="24" t="inlineStr">
+        <is>
+          <t>Alex Michelsen</t>
+        </is>
+      </c>
+      <c r="H27" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I27" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J27" s="25" t="n"/>
+      <c r="K27" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L27" s="26" t="n">
+        <v>144</v>
+      </c>
+      <c r="M27" s="27" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="N27" s="28" t="n">
+        <v>0.409836</v>
+      </c>
+      <c r="O27" s="28" t="n">
+        <v>0.657899</v>
+      </c>
+      <c r="P27" s="28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q27" s="28" t="n">
+        <v>0.248063</v>
+      </c>
+      <c r="R27" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S27" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T27" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U27" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V27" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W27" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y27" s="25" t="n"/>
+      <c r="Z27" s="26" t="n">
+        <v>144</v>
+      </c>
+      <c r="AA27" s="28" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AB27" s="28" t="n">
+        <v>0.000164</v>
+      </c>
+      <c r="AC27" s="30" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="AD27" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T00:20:17.768639Z</t>
+        </is>
+      </c>
+      <c r="AE27" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo on Hard: Francisco Cerundolo p=0.658 vs Alex Michelsen. Executable ask 0.4100 (aec-atp-alemic-fracer-2026-08-06).</t>
+        </is>
+      </c>
+      <c r="AF27" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo model; singles only, WTA+ATP market coverage, not yet locked-holdout qualified -- promoted by explicit operator directive, not genuine walk-forward validation.</t>
+        </is>
+      </c>
+      <c r="AG27" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH27" s="24" t="n"/>
+      <c r="AI27" s="31" t="n"/>
+      <c r="AJ27" s="31" t="n"/>
+      <c r="AK27" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL27" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM27" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN27" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO27" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP27" s="24" t="inlineStr">
+        <is>
+          <t>Francisco Cerundolo</t>
+        </is>
+      </c>
+      <c r="AQ27" s="24" t="inlineStr">
+        <is>
+          <t>Francisco Cerundolo</t>
+        </is>
+      </c>
+      <c r="AR27" s="24" t="inlineStr">
+        <is>
+          <t>Francisco Cerundolo</t>
+        </is>
+      </c>
+      <c r="AS27" s="24" t="inlineStr">
+        <is>
+          <t>Alex Michelsen</t>
+        </is>
+      </c>
+      <c r="AT27" s="24" t="inlineStr">
+        <is>
+          <t>Alex Michelsen</t>
+        </is>
+      </c>
+      <c r="AU27" s="24" t="inlineStr">
+        <is>
+          <t>Alex Michelsen</t>
+        </is>
+      </c>
+      <c r="AV27" s="24" t="n"/>
+      <c r="AW27" s="24" t="n"/>
+      <c r="AX27" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY27" s="24" t="n"/>
+      <c r="AZ27" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA27" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BB27" s="24" t="inlineStr">
+        <is>
+          <t>surface_blended_elo</t>
+        </is>
+      </c>
+      <c r="BC27" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD27" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BE27" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BF27" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG27" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BH27" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:02:18.609359Z</t>
+        </is>
+      </c>
+      <c r="BI27" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ27" s="25" t="n"/>
+      <c r="BK27" s="26" t="n">
+        <v>144</v>
+      </c>
+      <c r="BL27" s="27" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BM27" s="28" t="n">
+        <v>0.409836</v>
+      </c>
+      <c r="BN27" s="28" t="n"/>
+      <c r="BO27" s="28" t="n"/>
+      <c r="BP27" s="25" t="n"/>
+      <c r="BQ27" s="27" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BR27" s="28" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="BS27" s="28" t="n"/>
+      <c r="BT27" s="28" t="n"/>
+      <c r="BU27" s="25" t="n"/>
+      <c r="BV27" s="29" t="n"/>
+      <c r="BW27" s="24" t="n"/>
+      <c r="BX27" s="30" t="n"/>
+      <c r="BY27" s="27" t="n"/>
+      <c r="BZ27" s="24" t="n"/>
+      <c r="CA27" s="31" t="n"/>
+      <c r="CB27" s="24" t="n"/>
+      <c r="CC27" s="24" t="n"/>
+      <c r="CD27" s="24" t="n"/>
+      <c r="CE27" s="24" t="n"/>
+      <c r="CF27" s="24" t="n"/>
+      <c r="CG27" s="24" t="n"/>
+      <c r="CH27" s="24" t="n"/>
+      <c r="CI27" s="24" t="n"/>
+      <c r="CJ27" s="24" t="n"/>
+      <c r="CK27" s="24" t="n"/>
+      <c r="CL27" s="24" t="n"/>
+      <c r="CM27" s="24" t="n"/>
+      <c r="CN27" s="24" t="n"/>
+      <c r="CO27" s="24" t="n"/>
+      <c r="CP27" s="24" t="n"/>
+      <c r="CQ27" s="24" t="n"/>
+      <c r="CR27" s="24" t="n"/>
+      <c r="CS27" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>cbce5a7195d54c42</t>
+        </is>
+      </c>
+      <c r="B28" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:58:42.068094Z</t>
+        </is>
+      </c>
+      <c r="C28" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T21:00Z</t>
+        </is>
+      </c>
+      <c r="D28" s="24" t="inlineStr">
+        <is>
+          <t>421-2026:182193</t>
+        </is>
+      </c>
+      <c r="E28" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F28" s="24" t="inlineStr">
+        <is>
+          <t>Amanda Anisimova</t>
+        </is>
+      </c>
+      <c r="G28" s="24" t="inlineStr">
+        <is>
+          <t>Nikola Bartunkova</t>
+        </is>
+      </c>
+      <c r="H28" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I28" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J28" s="25" t="n"/>
+      <c r="K28" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L28" s="26" t="n">
+        <v>-194</v>
+      </c>
+      <c r="M28" s="27" t="n">
+        <v>1.515464</v>
+      </c>
+      <c r="N28" s="28" t="n">
+        <v>0.659864</v>
+      </c>
+      <c r="O28" s="28" t="n">
+        <v>0.7591</v>
+      </c>
+      <c r="P28" s="28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q28" s="28" t="n">
+        <v>0.099236</v>
+      </c>
+      <c r="R28" s="26" t="n">
+        <v>70</v>
+      </c>
+      <c r="S28" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T28" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U28" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V28" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W28" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X28" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="25" t="n"/>
+      <c r="Z28" s="26" t="n">
+        <v>-194</v>
+      </c>
+      <c r="AA28" s="28" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="AB28" s="28" t="n">
+        <v>0.000136</v>
+      </c>
+      <c r="AC28" s="30" t="n">
+        <v>1.0309</v>
+      </c>
+      <c r="AD28" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:06:22.233516Z</t>
+        </is>
+      </c>
+      <c r="AE28" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo on Hard: Amanda Anisimova p=0.759 vs Nikola Bartunkova. Executable ask 0.6600 (aec-wta-nikbar-amaani-2026-08-06).</t>
+        </is>
+      </c>
+      <c r="AF28" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo model; singles only, WTA+ATP market coverage, not yet locked-holdout qualified -- promoted by explicit operator directive, not genuine walk-forward validation.</t>
+        </is>
+      </c>
+      <c r="AG28" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH28" s="24" t="n"/>
+      <c r="AI28" s="31" t="n"/>
+      <c r="AJ28" s="31" t="n"/>
+      <c r="AK28" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL28" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM28" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN28" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO28" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP28" s="24" t="inlineStr">
+        <is>
+          <t>Amanda Anisimova</t>
+        </is>
+      </c>
+      <c r="AQ28" s="24" t="inlineStr">
+        <is>
+          <t>Amanda Anisimova</t>
+        </is>
+      </c>
+      <c r="AR28" s="24" t="inlineStr">
+        <is>
+          <t>Amanda Anisimova</t>
+        </is>
+      </c>
+      <c r="AS28" s="24" t="inlineStr">
+        <is>
+          <t>Nikola Bartunkova</t>
+        </is>
+      </c>
+      <c r="AT28" s="24" t="inlineStr">
+        <is>
+          <t>Nikola Bartunkova</t>
+        </is>
+      </c>
+      <c r="AU28" s="24" t="inlineStr">
+        <is>
+          <t>Nikola Bartunkova</t>
+        </is>
+      </c>
+      <c r="AV28" s="24" t="n"/>
+      <c r="AW28" s="24" t="n"/>
+      <c r="AX28" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY28" s="24" t="n"/>
+      <c r="AZ28" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA28" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BB28" s="24" t="inlineStr">
+        <is>
+          <t>surface_blended_elo</t>
+        </is>
+      </c>
+      <c r="BC28" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD28" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BE28" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BF28" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG28" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BH28" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:58:03.210799Z</t>
+        </is>
+      </c>
+      <c r="BI28" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ28" s="25" t="n"/>
+      <c r="BK28" s="26" t="n">
+        <v>-194</v>
+      </c>
+      <c r="BL28" s="27" t="n">
+        <v>1.515464</v>
+      </c>
+      <c r="BM28" s="28" t="n">
+        <v>0.659864</v>
+      </c>
+      <c r="BN28" s="28" t="n"/>
+      <c r="BO28" s="28" t="n"/>
+      <c r="BP28" s="25" t="n"/>
+      <c r="BQ28" s="27" t="n">
+        <v>1.515464</v>
+      </c>
+      <c r="BR28" s="28" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="BS28" s="28" t="n"/>
+      <c r="BT28" s="28" t="n"/>
+      <c r="BU28" s="25" t="n"/>
+      <c r="BV28" s="29" t="n"/>
+      <c r="BW28" s="24" t="n"/>
+      <c r="BX28" s="30" t="n"/>
+      <c r="BY28" s="27" t="n"/>
+      <c r="BZ28" s="24" t="n"/>
+      <c r="CA28" s="31" t="n"/>
+      <c r="CB28" s="24" t="n"/>
+      <c r="CC28" s="24" t="n"/>
+      <c r="CD28" s="24" t="n"/>
+      <c r="CE28" s="24" t="n"/>
+      <c r="CF28" s="24" t="n"/>
+      <c r="CG28" s="24" t="n"/>
+      <c r="CH28" s="24" t="n"/>
+      <c r="CI28" s="24" t="n"/>
+      <c r="CJ28" s="24" t="n"/>
+      <c r="CK28" s="24" t="n"/>
+      <c r="CL28" s="24" t="n"/>
+      <c r="CM28" s="24" t="n"/>
+      <c r="CN28" s="24" t="n"/>
+      <c r="CO28" s="24" t="n"/>
+      <c r="CP28" s="24" t="n"/>
+      <c r="CQ28" s="24" t="n"/>
+      <c r="CR28" s="24" t="n"/>
+      <c r="CS28" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>854a414968094de3</t>
+        </is>
+      </c>
+      <c r="B29" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:58:42.068094Z</t>
+        </is>
+      </c>
+      <c r="C29" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T23:00Z</t>
+        </is>
+      </c>
+      <c r="D29" s="24" t="inlineStr">
+        <is>
+          <t>421-2026:181763</t>
+        </is>
+      </c>
+      <c r="E29" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F29" s="24" t="inlineStr">
+        <is>
+          <t>Lorenzo Musetti</t>
+        </is>
+      </c>
+      <c r="G29" s="24" t="inlineStr">
+        <is>
+          <t>Rafael Jodar</t>
+        </is>
+      </c>
+      <c r="H29" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I29" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J29" s="25" t="n"/>
+      <c r="K29" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L29" s="26" t="n">
+        <v>127</v>
+      </c>
+      <c r="M29" s="27" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="N29" s="28" t="n">
+        <v>0.440529</v>
+      </c>
+      <c r="O29" s="28" t="n">
+        <v>0.544019</v>
+      </c>
+      <c r="P29" s="28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q29" s="28" t="n">
+        <v>0.10349</v>
+      </c>
+      <c r="R29" s="26" t="n">
+        <v>72</v>
+      </c>
+      <c r="S29" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T29" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U29" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V29" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W29" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y29" s="25" t="n"/>
+      <c r="Z29" s="26" t="n">
+        <v>127</v>
+      </c>
+      <c r="AA29" s="28" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AB29" s="28" t="n">
+        <v>-0.000529</v>
+      </c>
+      <c r="AC29" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD29" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:06:22.512232Z</t>
+        </is>
+      </c>
+      <c r="AE29" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo on Hard: Lorenzo Musetti p=0.544 vs Rafael Jodar. Executable ask 0.4400 (aec-atp-rafjod-lormus-2026-08-06).</t>
+        </is>
+      </c>
+      <c r="AF29" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo model; singles only, WTA+ATP market coverage, not yet locked-holdout qualified -- promoted by explicit operator directive, not genuine walk-forward validation.</t>
+        </is>
+      </c>
+      <c r="AG29" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH29" s="24" t="n"/>
+      <c r="AI29" s="31" t="n"/>
+      <c r="AJ29" s="31" t="n"/>
+      <c r="AK29" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL29" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM29" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN29" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO29" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP29" s="24" t="inlineStr">
+        <is>
+          <t>Lorenzo Musetti</t>
+        </is>
+      </c>
+      <c r="AQ29" s="24" t="inlineStr">
+        <is>
+          <t>Lorenzo Musetti</t>
+        </is>
+      </c>
+      <c r="AR29" s="24" t="inlineStr">
+        <is>
+          <t>Lorenzo Musetti</t>
+        </is>
+      </c>
+      <c r="AS29" s="24" t="inlineStr">
+        <is>
+          <t>Rafael Jodar</t>
+        </is>
+      </c>
+      <c r="AT29" s="24" t="inlineStr">
+        <is>
+          <t>Rafael Jodar</t>
+        </is>
+      </c>
+      <c r="AU29" s="24" t="inlineStr">
+        <is>
+          <t>Rafael Jodar</t>
+        </is>
+      </c>
+      <c r="AV29" s="24" t="n"/>
+      <c r="AW29" s="24" t="n"/>
+      <c r="AX29" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY29" s="24" t="n"/>
+      <c r="AZ29" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA29" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BB29" s="24" t="inlineStr">
+        <is>
+          <t>surface_blended_elo</t>
+        </is>
+      </c>
+      <c r="BC29" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD29" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BE29" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BF29" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG29" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BH29" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:58:10.033097Z</t>
+        </is>
+      </c>
+      <c r="BI29" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ29" s="25" t="n"/>
+      <c r="BK29" s="26" t="n">
+        <v>127</v>
+      </c>
+      <c r="BL29" s="27" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BM29" s="28" t="n">
+        <v>0.440529</v>
+      </c>
+      <c r="BN29" s="28" t="n"/>
+      <c r="BO29" s="28" t="n"/>
+      <c r="BP29" s="25" t="n"/>
+      <c r="BQ29" s="27" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BR29" s="28" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="BS29" s="28" t="n"/>
+      <c r="BT29" s="28" t="n"/>
+      <c r="BU29" s="25" t="n"/>
+      <c r="BV29" s="29" t="n"/>
+      <c r="BW29" s="24" t="n"/>
+      <c r="BX29" s="30" t="n"/>
+      <c r="BY29" s="27" t="n"/>
+      <c r="BZ29" s="24" t="n"/>
+      <c r="CA29" s="31" t="n"/>
+      <c r="CB29" s="24" t="n"/>
+      <c r="CC29" s="24" t="n"/>
+      <c r="CD29" s="24" t="n"/>
+      <c r="CE29" s="24" t="n"/>
+      <c r="CF29" s="24" t="n"/>
+      <c r="CG29" s="24" t="n"/>
+      <c r="CH29" s="24" t="n"/>
+      <c r="CI29" s="24" t="n"/>
+      <c r="CJ29" s="24" t="n"/>
+      <c r="CK29" s="24" t="n"/>
+      <c r="CL29" s="24" t="n"/>
+      <c r="CM29" s="24" t="n"/>
+      <c r="CN29" s="24" t="n"/>
+      <c r="CO29" s="24" t="n"/>
+      <c r="CP29" s="24" t="n"/>
+      <c r="CQ29" s="24" t="n"/>
+      <c r="CR29" s="24" t="n"/>
+      <c r="CS29" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>56254b0ff65c48f8</t>
+        </is>
+      </c>
+      <c r="B30" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:10:09.393141Z</t>
+        </is>
+      </c>
+      <c r="C30" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T10:00Z</t>
+        </is>
+      </c>
+      <c r="D30" s="24" t="inlineStr">
+        <is>
+          <t>961-2026:182110</t>
+        </is>
+      </c>
+      <c r="E30" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F30" s="24" t="inlineStr">
+        <is>
+          <t>Gabriela Knutson</t>
+        </is>
+      </c>
+      <c r="G30" s="24" t="inlineStr">
+        <is>
+          <t>Elizara Yaneva</t>
+        </is>
+      </c>
+      <c r="H30" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I30" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J30" s="25" t="n"/>
+      <c r="K30" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L30" s="26" t="n">
+        <v>138</v>
+      </c>
+      <c r="M30" s="27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="N30" s="28" t="n">
+        <v>0.420168</v>
+      </c>
+      <c r="O30" s="28" t="n">
+        <v>0.551853</v>
+      </c>
+      <c r="P30" s="28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q30" s="28" t="n">
+        <v>0.131685</v>
+      </c>
+      <c r="R30" s="26" t="n">
+        <v>86</v>
+      </c>
+      <c r="S30" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T30" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U30" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V30" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W30" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X30" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="25" t="n"/>
+      <c r="Z30" s="26" t="n">
+        <v>138</v>
+      </c>
+      <c r="AA30" s="28" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AB30" s="28" t="n">
+        <v>-0.000168</v>
+      </c>
+      <c r="AC30" s="30" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AD30" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T12:12:32.744915Z</t>
+        </is>
+      </c>
+      <c r="AE30" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo on Hard: Gabriela Knutson p=0.552 vs Elizara Yaneva. Executable ask 0.4200 (aec-wta-eliyan-gabknu-2026-08-07).</t>
+        </is>
+      </c>
+      <c r="AF30" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo model; singles only, WTA+ATP market coverage, not yet locked-holdout qualified -- promoted by explicit operator directive, not genuine walk-forward validation.</t>
+        </is>
+      </c>
+      <c r="AG30" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH30" s="24" t="n"/>
+      <c r="AI30" s="31" t="n"/>
+      <c r="AJ30" s="31" t="n"/>
+      <c r="AK30" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL30" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM30" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN30" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO30" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP30" s="24" t="inlineStr">
+        <is>
+          <t>Gabriela Knutson</t>
+        </is>
+      </c>
+      <c r="AQ30" s="24" t="inlineStr">
+        <is>
+          <t>Gabriela Knutson</t>
+        </is>
+      </c>
+      <c r="AR30" s="24" t="inlineStr">
+        <is>
+          <t>Gabriela Knutson</t>
+        </is>
+      </c>
+      <c r="AS30" s="24" t="inlineStr">
+        <is>
+          <t>Elizara Yaneva</t>
+        </is>
+      </c>
+      <c r="AT30" s="24" t="inlineStr">
+        <is>
+          <t>Elizara Yaneva</t>
+        </is>
+      </c>
+      <c r="AU30" s="24" t="inlineStr">
+        <is>
+          <t>Elizara Yaneva</t>
+        </is>
+      </c>
+      <c r="AV30" s="24" t="n"/>
+      <c r="AW30" s="24" t="n"/>
+      <c r="AX30" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY30" s="24" t="n"/>
+      <c r="AZ30" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA30" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BB30" s="24" t="inlineStr">
+        <is>
+          <t>surface_blended_elo</t>
+        </is>
+      </c>
+      <c r="BC30" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD30" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BE30" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BF30" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG30" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BH30" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:08:50.003635Z</t>
+        </is>
+      </c>
+      <c r="BI30" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ30" s="25" t="n"/>
+      <c r="BK30" s="26" t="n">
+        <v>138</v>
+      </c>
+      <c r="BL30" s="27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BM30" s="28" t="n">
+        <v>0.420168</v>
+      </c>
+      <c r="BN30" s="28" t="n"/>
+      <c r="BO30" s="28" t="n"/>
+      <c r="BP30" s="25" t="n"/>
+      <c r="BQ30" s="27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BR30" s="28" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="BS30" s="28" t="n"/>
+      <c r="BT30" s="28" t="n"/>
+      <c r="BU30" s="25" t="n"/>
+      <c r="BV30" s="29" t="n"/>
+      <c r="BW30" s="24" t="n"/>
+      <c r="BX30" s="30" t="n"/>
+      <c r="BY30" s="27" t="n"/>
+      <c r="BZ30" s="24" t="n"/>
+      <c r="CA30" s="31" t="n"/>
+      <c r="CB30" s="24" t="n"/>
+      <c r="CC30" s="24" t="n"/>
+      <c r="CD30" s="24" t="n"/>
+      <c r="CE30" s="24" t="n"/>
+      <c r="CF30" s="24" t="n"/>
+      <c r="CG30" s="24" t="n"/>
+      <c r="CH30" s="24" t="n"/>
+      <c r="CI30" s="24" t="n"/>
+      <c r="CJ30" s="24" t="n"/>
+      <c r="CK30" s="24" t="n"/>
+      <c r="CL30" s="24" t="n"/>
+      <c r="CM30" s="24" t="n"/>
+      <c r="CN30" s="24" t="n"/>
+      <c r="CO30" s="24" t="n"/>
+      <c r="CP30" s="24" t="n"/>
+      <c r="CQ30" s="24" t="n"/>
+      <c r="CR30" s="24" t="n"/>
+      <c r="CS30" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="36" customHeight="1">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>4ae706cb87284e44</t>
+        </is>
+      </c>
+      <c r="B31" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T21:56:48.826537Z</t>
+        </is>
+      </c>
+      <c r="C31" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T23:30Z</t>
+        </is>
+      </c>
+      <c r="D31" s="24" t="inlineStr">
+        <is>
+          <t>421-2026:181766</t>
+        </is>
+      </c>
+      <c r="E31" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F31" s="24" t="inlineStr">
+        <is>
+          <t>Thiago Agustin Tirante</t>
+        </is>
+      </c>
+      <c r="G31" s="24" t="inlineStr">
+        <is>
+          <t>Alexei Popyrin</t>
+        </is>
+      </c>
+      <c r="H31" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I31" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J31" s="25" t="n"/>
+      <c r="K31" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L31" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="M31" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="N31" s="28" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="O31" s="28" t="n">
+        <v>0.592411</v>
+      </c>
+      <c r="P31" s="28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q31" s="28" t="n">
+        <v>0.141961</v>
+      </c>
+      <c r="R31" s="26" t="n">
+        <v>91</v>
+      </c>
+      <c r="S31" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T31" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U31" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V31" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W31" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X31" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="25" t="n"/>
+      <c r="Z31" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="AA31" s="28" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AB31" s="28" t="n">
+        <v>-0.00045</v>
+      </c>
+      <c r="AC31" s="30" t="n">
+        <v>1.525</v>
+      </c>
+      <c r="AD31" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-08T04:03:11.057660Z</t>
+        </is>
+      </c>
+      <c r="AE31" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo on Hard: Thiago Agustin Tirante p=0.592 vs Alexei Popyrin. Executable ask 0.4500 (aec-atp-alepop-thitir-2026-08-06).</t>
+        </is>
+      </c>
+      <c r="AF31" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo model; singles only, WTA+ATP market coverage, not yet locked-holdout qualified -- promoted by explicit operator directive, not genuine walk-forward validation.</t>
+        </is>
+      </c>
+      <c r="AG31" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH31" s="24" t="n"/>
+      <c r="AI31" s="31" t="n"/>
+      <c r="AJ31" s="31" t="n"/>
+      <c r="AK31" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL31" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM31" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN31" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO31" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP31" s="24" t="inlineStr">
+        <is>
+          <t>Thiago Agustin Tirante</t>
+        </is>
+      </c>
+      <c r="AQ31" s="24" t="inlineStr">
+        <is>
+          <t>Thiago Agustin Tirante</t>
+        </is>
+      </c>
+      <c r="AR31" s="24" t="inlineStr">
+        <is>
+          <t>Thiago Agustin Tirante</t>
+        </is>
+      </c>
+      <c r="AS31" s="24" t="inlineStr">
+        <is>
+          <t>Alexei Popyrin</t>
+        </is>
+      </c>
+      <c r="AT31" s="24" t="inlineStr">
+        <is>
+          <t>Alexei Popyrin</t>
+        </is>
+      </c>
+      <c r="AU31" s="24" t="inlineStr">
+        <is>
+          <t>Alexei Popyrin</t>
+        </is>
+      </c>
+      <c r="AV31" s="24" t="n"/>
+      <c r="AW31" s="24" t="n"/>
+      <c r="AX31" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY31" s="24" t="n"/>
+      <c r="AZ31" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA31" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BB31" s="24" t="inlineStr">
+        <is>
+          <t>surface_blended_elo</t>
+        </is>
+      </c>
+      <c r="BC31" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD31" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BE31" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BF31" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG31" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BH31" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T21:56:07.767044Z</t>
+        </is>
+      </c>
+      <c r="BI31" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ31" s="25" t="n"/>
+      <c r="BK31" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="BL31" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BM31" s="28" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="BN31" s="28" t="n"/>
+      <c r="BO31" s="28" t="n"/>
+      <c r="BP31" s="25" t="n"/>
+      <c r="BQ31" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BR31" s="28" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="BS31" s="28" t="n"/>
+      <c r="BT31" s="28" t="n"/>
+      <c r="BU31" s="25" t="n"/>
+      <c r="BV31" s="29" t="n"/>
+      <c r="BW31" s="24" t="n"/>
+      <c r="BX31" s="30" t="n"/>
+      <c r="BY31" s="27" t="n"/>
+      <c r="BZ31" s="24" t="n"/>
+      <c r="CA31" s="31" t="n"/>
+      <c r="CB31" s="24" t="n"/>
+      <c r="CC31" s="24" t="n"/>
+      <c r="CD31" s="24" t="n"/>
+      <c r="CE31" s="24" t="n"/>
+      <c r="CF31" s="24" t="n"/>
+      <c r="CG31" s="24" t="n"/>
+      <c r="CH31" s="24" t="n"/>
+      <c r="CI31" s="24" t="n"/>
+      <c r="CJ31" s="24" t="n"/>
+      <c r="CK31" s="24" t="n"/>
+      <c r="CL31" s="24" t="n"/>
+      <c r="CM31" s="24" t="n"/>
+      <c r="CN31" s="24" t="n"/>
+      <c r="CO31" s="24" t="n"/>
+      <c r="CP31" s="24" t="n"/>
+      <c r="CQ31" s="24" t="n"/>
+      <c r="CR31" s="24" t="n"/>
+      <c r="CS31" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>a364612e1095454b</t>
+        </is>
+      </c>
+      <c r="B32" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T14:00:10.713543Z</t>
+        </is>
+      </c>
+      <c r="C32" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T16:30Z</t>
+        </is>
+      </c>
+      <c r="D32" s="24" t="inlineStr">
+        <is>
+          <t>421-2026:182177</t>
+        </is>
+      </c>
+      <c r="E32" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F32" s="24" t="inlineStr">
+        <is>
+          <t>Elena Rybakina</t>
+        </is>
+      </c>
+      <c r="G32" s="24" t="inlineStr">
+        <is>
+          <t>Liudmila Samsonova</t>
+        </is>
+      </c>
+      <c r="H32" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I32" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J32" s="25" t="n"/>
+      <c r="K32" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L32" s="26" t="n">
+        <v>-300</v>
+      </c>
+      <c r="M32" s="27" t="n">
+        <v>1.333333</v>
+      </c>
+      <c r="N32" s="28" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="O32" s="28" t="n">
+        <v>0.9112749999999999</v>
+      </c>
+      <c r="P32" s="28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q32" s="28" t="n">
+        <v>0.161275</v>
+      </c>
+      <c r="R32" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S32" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T32" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U32" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V32" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W32" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X32" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="25" t="n"/>
+      <c r="Z32" s="26" t="n">
+        <v>-300</v>
+      </c>
+      <c r="AA32" s="28" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AB32" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="30" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="AD32" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T20:24:26.522023Z</t>
+        </is>
+      </c>
+      <c r="AE32" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo on Hard: Elena Rybakina p=0.911 vs Liudmila Samsonova. Executable ask 0.7500 (aec-wta-liusam-eleryb-2026-08-09).</t>
+        </is>
+      </c>
+      <c r="AF32" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo model; singles only, WTA+ATP market coverage, not yet locked-holdout qualified -- promoted by explicit operator directive, not genuine walk-forward validation.</t>
+        </is>
+      </c>
+      <c r="AG32" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH32" s="24" t="n"/>
+      <c r="AI32" s="31" t="n"/>
+      <c r="AJ32" s="31" t="n"/>
+      <c r="AK32" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL32" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM32" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN32" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO32" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP32" s="24" t="inlineStr">
+        <is>
+          <t>Elena Rybakina</t>
+        </is>
+      </c>
+      <c r="AQ32" s="24" t="inlineStr">
+        <is>
+          <t>Elena Rybakina</t>
+        </is>
+      </c>
+      <c r="AR32" s="24" t="inlineStr">
+        <is>
+          <t>Elena Rybakina</t>
+        </is>
+      </c>
+      <c r="AS32" s="24" t="inlineStr">
+        <is>
+          <t>Liudmila Samsonova</t>
+        </is>
+      </c>
+      <c r="AT32" s="24" t="inlineStr">
+        <is>
+          <t>Liudmila Samsonova</t>
+        </is>
+      </c>
+      <c r="AU32" s="24" t="inlineStr">
+        <is>
+          <t>Liudmila Samsonova</t>
+        </is>
+      </c>
+      <c r="AV32" s="24" t="n"/>
+      <c r="AW32" s="24" t="n"/>
+      <c r="AX32" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY32" s="24" t="n"/>
+      <c r="AZ32" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA32" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BB32" s="24" t="inlineStr">
+        <is>
+          <t>surface_blended_elo</t>
+        </is>
+      </c>
+      <c r="BC32" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD32" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BE32" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BF32" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG32" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BH32" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T13:58:22.617706Z</t>
+        </is>
+      </c>
+      <c r="BI32" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ32" s="25" t="n"/>
+      <c r="BK32" s="26" t="n">
+        <v>-300</v>
+      </c>
+      <c r="BL32" s="27" t="n">
+        <v>1.333333</v>
+      </c>
+      <c r="BM32" s="28" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BN32" s="28" t="n"/>
+      <c r="BO32" s="28" t="n"/>
+      <c r="BP32" s="25" t="n"/>
+      <c r="BQ32" s="27" t="n">
+        <v>1.333333</v>
+      </c>
+      <c r="BR32" s="28" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BS32" s="28" t="n"/>
+      <c r="BT32" s="28" t="n"/>
+      <c r="BU32" s="25" t="n"/>
+      <c r="BV32" s="29" t="n"/>
+      <c r="BW32" s="24" t="n"/>
+      <c r="BX32" s="30" t="n"/>
+      <c r="BY32" s="27" t="n"/>
+      <c r="BZ32" s="24" t="n"/>
+      <c r="CA32" s="31" t="n"/>
+      <c r="CB32" s="24" t="n"/>
+      <c r="CC32" s="24" t="n"/>
+      <c r="CD32" s="24" t="n"/>
+      <c r="CE32" s="24" t="n"/>
+      <c r="CF32" s="24" t="n"/>
+      <c r="CG32" s="24" t="n"/>
+      <c r="CH32" s="24" t="n"/>
+      <c r="CI32" s="24" t="n"/>
+      <c r="CJ32" s="24" t="n"/>
+      <c r="CK32" s="24" t="n"/>
+      <c r="CL32" s="24" t="n"/>
+      <c r="CM32" s="24" t="n"/>
+      <c r="CN32" s="24" t="n"/>
+      <c r="CO32" s="24" t="n"/>
+      <c r="CP32" s="24" t="n"/>
+      <c r="CQ32" s="24" t="n"/>
+      <c r="CR32" s="24" t="n"/>
+      <c r="CS32" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="36" customHeight="1">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>8e56cc99125a4404</t>
+        </is>
+      </c>
+      <c r="B33" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T14:00:10.713543Z</t>
+        </is>
+      </c>
+      <c r="C33" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T16:30Z</t>
+        </is>
+      </c>
+      <c r="D33" s="24" t="inlineStr">
+        <is>
+          <t>421-2026:181739</t>
+        </is>
+      </c>
+      <c r="E33" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F33" s="24" t="inlineStr">
+        <is>
+          <t>Daniel Merida</t>
+        </is>
+      </c>
+      <c r="G33" s="24" t="inlineStr">
+        <is>
+          <t>Tallon Griekspoor</t>
+        </is>
+      </c>
+      <c r="H33" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I33" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J33" s="25" t="n"/>
+      <c r="K33" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L33" s="26" t="n">
+        <v>117</v>
+      </c>
+      <c r="M33" s="27" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="N33" s="28" t="n">
+        <v>0.460829</v>
+      </c>
+      <c r="O33" s="28" t="n">
+        <v>0.5573360000000001</v>
+      </c>
+      <c r="P33" s="28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q33" s="28" t="n">
+        <v>0.096507</v>
+      </c>
+      <c r="R33" s="26" t="n">
+        <v>68</v>
+      </c>
+      <c r="S33" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T33" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U33" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V33" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W33" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X33" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" s="25" t="n"/>
+      <c r="Z33" s="26" t="n">
+        <v>117</v>
+      </c>
+      <c r="AA33" s="28" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AB33" s="28" t="n">
+        <v>-0.000829</v>
+      </c>
+      <c r="AC33" s="30" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AD33" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T20:24:26.781078Z</t>
+        </is>
+      </c>
+      <c r="AE33" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo on Hard: Daniel Merida p=0.557 vs Tallon Griekspoor. Executable ask 0.4600 (aec-atp-talgri-danagu-2026-08-08).</t>
+        </is>
+      </c>
+      <c r="AF33" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo model; singles only, WTA+ATP market coverage, not yet locked-holdout qualified -- promoted by explicit operator directive, not genuine walk-forward validation.</t>
+        </is>
+      </c>
+      <c r="AG33" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH33" s="24" t="n"/>
+      <c r="AI33" s="31" t="n"/>
+      <c r="AJ33" s="31" t="n"/>
+      <c r="AK33" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL33" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM33" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN33" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO33" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP33" s="24" t="inlineStr">
+        <is>
+          <t>Daniel Merida</t>
+        </is>
+      </c>
+      <c r="AQ33" s="24" t="inlineStr">
+        <is>
+          <t>Daniel Merida</t>
+        </is>
+      </c>
+      <c r="AR33" s="24" t="inlineStr">
+        <is>
+          <t>Daniel Merida</t>
+        </is>
+      </c>
+      <c r="AS33" s="24" t="inlineStr">
+        <is>
+          <t>Tallon Griekspoor</t>
+        </is>
+      </c>
+      <c r="AT33" s="24" t="inlineStr">
+        <is>
+          <t>Tallon Griekspoor</t>
+        </is>
+      </c>
+      <c r="AU33" s="24" t="inlineStr">
+        <is>
+          <t>Tallon Griekspoor</t>
+        </is>
+      </c>
+      <c r="AV33" s="24" t="n"/>
+      <c r="AW33" s="24" t="n"/>
+      <c r="AX33" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY33" s="24" t="n"/>
+      <c r="AZ33" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA33" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BB33" s="24" t="inlineStr">
+        <is>
+          <t>surface_blended_elo</t>
+        </is>
+      </c>
+      <c r="BC33" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD33" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BE33" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BF33" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG33" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BH33" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T13:58:24.994988Z</t>
+        </is>
+      </c>
+      <c r="BI33" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ33" s="25" t="n"/>
+      <c r="BK33" s="26" t="n">
+        <v>117</v>
+      </c>
+      <c r="BL33" s="27" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BM33" s="28" t="n">
+        <v>0.460829</v>
+      </c>
+      <c r="BN33" s="28" t="n"/>
+      <c r="BO33" s="28" t="n"/>
+      <c r="BP33" s="25" t="n"/>
+      <c r="BQ33" s="27" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BR33" s="28" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="BS33" s="28" t="n"/>
+      <c r="BT33" s="28" t="n"/>
+      <c r="BU33" s="25" t="n"/>
+      <c r="BV33" s="29" t="n"/>
+      <c r="BW33" s="24" t="n"/>
+      <c r="BX33" s="30" t="n"/>
+      <c r="BY33" s="27" t="n"/>
+      <c r="BZ33" s="24" t="n"/>
+      <c r="CA33" s="31" t="n"/>
+      <c r="CB33" s="24" t="n"/>
+      <c r="CC33" s="24" t="n"/>
+      <c r="CD33" s="24" t="n"/>
+      <c r="CE33" s="24" t="n"/>
+      <c r="CF33" s="24" t="n"/>
+      <c r="CG33" s="24" t="n"/>
+      <c r="CH33" s="24" t="n"/>
+      <c r="CI33" s="24" t="n"/>
+      <c r="CJ33" s="24" t="n"/>
+      <c r="CK33" s="24" t="n"/>
+      <c r="CL33" s="24" t="n"/>
+      <c r="CM33" s="24" t="n"/>
+      <c r="CN33" s="24" t="n"/>
+      <c r="CO33" s="24" t="n"/>
+      <c r="CP33" s="24" t="n"/>
+      <c r="CQ33" s="24" t="n"/>
+      <c r="CR33" s="24" t="n"/>
+      <c r="CS33" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="36" customHeight="1">
+      <c r="A34" s="24" t="inlineStr">
+        <is>
+          <t>fe273b8f60d24457</t>
+        </is>
+      </c>
+      <c r="B34" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T17:06:49.007603Z</t>
+        </is>
+      </c>
+      <c r="C34" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T18:00Z</t>
+        </is>
+      </c>
+      <c r="D34" s="24" t="inlineStr">
+        <is>
+          <t>421-2026:182197</t>
+        </is>
+      </c>
+      <c r="E34" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F34" s="24" t="inlineStr">
+        <is>
+          <t>Coco Gauff</t>
+        </is>
+      </c>
+      <c r="G34" s="24" t="inlineStr">
+        <is>
+          <t>Alina Korneeva</t>
+        </is>
+      </c>
+      <c r="H34" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I34" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J34" s="25" t="n"/>
+      <c r="K34" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L34" s="26" t="n">
+        <v>-317</v>
+      </c>
+      <c r="M34" s="27" t="n">
+        <v>1.315457</v>
+      </c>
+      <c r="N34" s="28" t="n">
+        <v>0.760192</v>
+      </c>
+      <c r="O34" s="28" t="n">
+        <v>0.846981</v>
+      </c>
+      <c r="P34" s="28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q34" s="28" t="n">
+        <v>0.08678900000000001</v>
+      </c>
+      <c r="R34" s="26" t="n">
+        <v>63</v>
+      </c>
+      <c r="S34" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T34" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U34" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V34" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W34" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X34" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="25" t="n"/>
+      <c r="Z34" s="26" t="n">
+        <v>-317</v>
+      </c>
+      <c r="AA34" s="28" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AB34" s="28" t="n">
+        <v>-0.000192</v>
+      </c>
+      <c r="AC34" s="30" t="n">
+        <v>0.6309</v>
+      </c>
+      <c r="AD34" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T23:28:59.274460Z</t>
+        </is>
+      </c>
+      <c r="AE34" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo on Hard: Coco Gauff p=0.847 vs Alina Korneeva. Executable ask 0.7600 (aec-wta-alikor-cocgau-2026-08-09).</t>
+        </is>
+      </c>
+      <c r="AF34" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo model; singles only, WTA+ATP market coverage, not yet locked-holdout qualified -- promoted by explicit operator directive, not genuine walk-forward validation.</t>
+        </is>
+      </c>
+      <c r="AG34" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH34" s="24" t="n"/>
+      <c r="AI34" s="31" t="n"/>
+      <c r="AJ34" s="31" t="n"/>
+      <c r="AK34" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL34" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM34" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN34" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO34" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP34" s="24" t="inlineStr">
+        <is>
+          <t>Coco Gauff</t>
+        </is>
+      </c>
+      <c r="AQ34" s="24" t="inlineStr">
+        <is>
+          <t>Coco Gauff</t>
+        </is>
+      </c>
+      <c r="AR34" s="24" t="inlineStr">
+        <is>
+          <t>Coco Gauff</t>
+        </is>
+      </c>
+      <c r="AS34" s="24" t="inlineStr">
+        <is>
+          <t>Alina Korneeva</t>
+        </is>
+      </c>
+      <c r="AT34" s="24" t="inlineStr">
+        <is>
+          <t>Alina Korneeva</t>
+        </is>
+      </c>
+      <c r="AU34" s="24" t="inlineStr">
+        <is>
+          <t>Alina Korneeva</t>
+        </is>
+      </c>
+      <c r="AV34" s="24" t="n"/>
+      <c r="AW34" s="24" t="n"/>
+      <c r="AX34" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY34" s="24" t="n"/>
+      <c r="AZ34" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA34" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BB34" s="24" t="inlineStr">
+        <is>
+          <t>surface_blended_elo</t>
+        </is>
+      </c>
+      <c r="BC34" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD34" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BE34" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BF34" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG34" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BH34" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T17:05:49.061688Z</t>
+        </is>
+      </c>
+      <c r="BI34" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ34" s="25" t="n"/>
+      <c r="BK34" s="26" t="n">
+        <v>-317</v>
+      </c>
+      <c r="BL34" s="27" t="n">
+        <v>1.315457</v>
+      </c>
+      <c r="BM34" s="28" t="n">
+        <v>0.760192</v>
+      </c>
+      <c r="BN34" s="28" t="n"/>
+      <c r="BO34" s="28" t="n"/>
+      <c r="BP34" s="25" t="n"/>
+      <c r="BQ34" s="27" t="n">
+        <v>1.315457</v>
+      </c>
+      <c r="BR34" s="28" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="BS34" s="28" t="n"/>
+      <c r="BT34" s="28" t="n"/>
+      <c r="BU34" s="25" t="n"/>
+      <c r="BV34" s="29" t="n"/>
+      <c r="BW34" s="24" t="n"/>
+      <c r="BX34" s="30" t="n"/>
+      <c r="BY34" s="27" t="n"/>
+      <c r="BZ34" s="24" t="n"/>
+      <c r="CA34" s="31" t="n"/>
+      <c r="CB34" s="24" t="n"/>
+      <c r="CC34" s="24" t="n"/>
+      <c r="CD34" s="24" t="n"/>
+      <c r="CE34" s="24" t="n"/>
+      <c r="CF34" s="24" t="n"/>
+      <c r="CG34" s="24" t="n"/>
+      <c r="CH34" s="24" t="n"/>
+      <c r="CI34" s="24" t="n"/>
+      <c r="CJ34" s="24" t="n"/>
+      <c r="CK34" s="24" t="n"/>
+      <c r="CL34" s="24" t="n"/>
+      <c r="CM34" s="24" t="n"/>
+      <c r="CN34" s="24" t="n"/>
+      <c r="CO34" s="24" t="n"/>
+      <c r="CP34" s="24" t="n"/>
+      <c r="CQ34" s="24" t="n"/>
+      <c r="CR34" s="24" t="n"/>
+      <c r="CS34" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="36" customHeight="1">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>2e228163a3ae43db</t>
+        </is>
+      </c>
+      <c r="B35" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T20:27:13.230036Z</t>
+        </is>
+      </c>
+      <c r="C35" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T22:00Z</t>
+        </is>
+      </c>
+      <c r="D35" s="24" t="inlineStr">
+        <is>
+          <t>421-2026:181772</t>
+        </is>
+      </c>
+      <c r="E35" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F35" s="24" t="inlineStr">
+        <is>
+          <t>Ben Shelton</t>
+        </is>
+      </c>
+      <c r="G35" s="24" t="inlineStr">
+        <is>
+          <t>Joao Fonseca</t>
+        </is>
+      </c>
+      <c r="H35" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I35" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J35" s="25" t="n"/>
+      <c r="K35" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L35" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="M35" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="N35" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="O35" s="28" t="n">
+        <v>0.620733</v>
+      </c>
+      <c r="P35" s="28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q35" s="28" t="n">
+        <v>0.061262</v>
+      </c>
+      <c r="R35" s="26" t="n">
+        <v>51</v>
+      </c>
+      <c r="S35" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T35" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U35" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V35" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W35" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X35" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" s="25" t="n"/>
+      <c r="Z35" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="AA35" s="28" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AB35" s="28" t="n">
+        <v>0.000529</v>
+      </c>
+      <c r="AC35" s="30" t="n">
+        <v>1.1811</v>
+      </c>
+      <c r="AD35" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-10T02:33:54.286304Z</t>
+        </is>
+      </c>
+      <c r="AE35" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo on Hard: Ben Shelton p=0.621 vs Joao Fonseca. Executable ask 0.5600 (aec-atp-joafon-benshe-2026-08-10).</t>
+        </is>
+      </c>
+      <c r="AF35" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo model; singles only, WTA+ATP market coverage, not yet locked-holdout qualified -- promoted by explicit operator directive, not genuine walk-forward validation.</t>
+        </is>
+      </c>
+      <c r="AG35" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH35" s="24" t="n"/>
+      <c r="AI35" s="31" t="n"/>
+      <c r="AJ35" s="31" t="n"/>
+      <c r="AK35" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL35" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM35" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN35" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO35" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP35" s="24" t="inlineStr">
+        <is>
+          <t>Ben Shelton</t>
+        </is>
+      </c>
+      <c r="AQ35" s="24" t="inlineStr">
+        <is>
+          <t>Ben Shelton</t>
+        </is>
+      </c>
+      <c r="AR35" s="24" t="inlineStr">
+        <is>
+          <t>Ben Shelton</t>
+        </is>
+      </c>
+      <c r="AS35" s="24" t="inlineStr">
+        <is>
+          <t>Joao Fonseca</t>
+        </is>
+      </c>
+      <c r="AT35" s="24" t="inlineStr">
+        <is>
+          <t>Joao Fonseca</t>
+        </is>
+      </c>
+      <c r="AU35" s="24" t="inlineStr">
+        <is>
+          <t>Joao Fonseca</t>
+        </is>
+      </c>
+      <c r="AV35" s="24" t="n"/>
+      <c r="AW35" s="24" t="n"/>
+      <c r="AX35" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY35" s="24" t="n"/>
+      <c r="AZ35" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA35" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BB35" s="24" t="inlineStr">
+        <is>
+          <t>surface_blended_elo</t>
+        </is>
+      </c>
+      <c r="BC35" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD35" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BE35" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BF35" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG35" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BH35" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T20:26:49.889205Z</t>
+        </is>
+      </c>
+      <c r="BI35" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ35" s="25" t="n"/>
+      <c r="BK35" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="BL35" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="BM35" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="BN35" s="28" t="n"/>
+      <c r="BO35" s="28" t="n"/>
+      <c r="BP35" s="25" t="n"/>
+      <c r="BQ35" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="BR35" s="28" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="BS35" s="28" t="n"/>
+      <c r="BT35" s="28" t="n"/>
+      <c r="BU35" s="25" t="n"/>
+      <c r="BV35" s="29" t="n"/>
+      <c r="BW35" s="24" t="n"/>
+      <c r="BX35" s="30" t="n"/>
+      <c r="BY35" s="27" t="n"/>
+      <c r="BZ35" s="24" t="n"/>
+      <c r="CA35" s="31" t="n"/>
+      <c r="CB35" s="24" t="n"/>
+      <c r="CC35" s="24" t="n"/>
+      <c r="CD35" s="24" t="n"/>
+      <c r="CE35" s="24" t="n"/>
+      <c r="CF35" s="24" t="n"/>
+      <c r="CG35" s="24" t="n"/>
+      <c r="CH35" s="24" t="n"/>
+      <c r="CI35" s="24" t="n"/>
+      <c r="CJ35" s="24" t="n"/>
+      <c r="CK35" s="24" t="n"/>
+      <c r="CL35" s="24" t="n"/>
+      <c r="CM35" s="24" t="n"/>
+      <c r="CN35" s="24" t="n"/>
+      <c r="CO35" s="24" t="n"/>
+      <c r="CP35" s="24" t="n"/>
+      <c r="CQ35" s="24" t="n"/>
+      <c r="CR35" s="24" t="n"/>
+      <c r="CS35" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="36" customHeight="1">
+      <c r="A36" s="24" t="inlineStr">
+        <is>
+          <t>6725e3e0f7d2467e</t>
+        </is>
+      </c>
+      <c r="B36" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T23:32:17.957013Z</t>
+        </is>
+      </c>
+      <c r="C36" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-10T00:30Z</t>
+        </is>
+      </c>
+      <c r="D36" s="24" t="inlineStr">
+        <is>
+          <t>421-2026:182189</t>
+        </is>
+      </c>
+      <c r="E36" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F36" s="24" t="inlineStr">
+        <is>
+          <t>Belinda Bencic</t>
+        </is>
+      </c>
+      <c r="G36" s="24" t="inlineStr">
+        <is>
+          <t>Alexandra Eala</t>
+        </is>
+      </c>
+      <c r="H36" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I36" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J36" s="25" t="n"/>
+      <c r="K36" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L36" s="26" t="n">
+        <v>-117</v>
+      </c>
+      <c r="M36" s="27" t="n">
+        <v>1.854701</v>
+      </c>
+      <c r="N36" s="28" t="n">
+        <v>0.539171</v>
+      </c>
+      <c r="O36" s="28" t="n">
+        <v>0.646782</v>
+      </c>
+      <c r="P36" s="28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q36" s="28" t="n">
+        <v>0.107611</v>
+      </c>
+      <c r="R36" s="26" t="n">
+        <v>74</v>
+      </c>
+      <c r="S36" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T36" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U36" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V36" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W36" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X36" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" s="25" t="n"/>
+      <c r="Z36" s="26" t="n">
+        <v>-117</v>
+      </c>
+      <c r="AA36" s="28" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AB36" s="28" t="n">
+        <v>0.000829</v>
+      </c>
+      <c r="AC36" s="30" t="n">
+        <v>1.4957</v>
+      </c>
+      <c r="AD36" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-10T02:33:54.881626Z</t>
+        </is>
+      </c>
+      <c r="AE36" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo on Hard: Belinda Bencic p=0.647 vs Alexandra Eala. Executable ask 0.5400 (aec-wta-aleeal-belben-2026-08-09).</t>
+        </is>
+      </c>
+      <c r="AF36" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo model; singles only, WTA+ATP market coverage, not yet locked-holdout qualified -- promoted by explicit operator directive, not genuine walk-forward validation.</t>
+        </is>
+      </c>
+      <c r="AG36" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH36" s="24" t="n"/>
+      <c r="AI36" s="31" t="n"/>
+      <c r="AJ36" s="31" t="n"/>
+      <c r="AK36" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL36" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM36" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN36" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO36" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP36" s="24" t="inlineStr">
+        <is>
+          <t>Belinda Bencic</t>
+        </is>
+      </c>
+      <c r="AQ36" s="24" t="inlineStr">
+        <is>
+          <t>Belinda Bencic</t>
+        </is>
+      </c>
+      <c r="AR36" s="24" t="inlineStr">
+        <is>
+          <t>Belinda Bencic</t>
+        </is>
+      </c>
+      <c r="AS36" s="24" t="inlineStr">
+        <is>
+          <t>Alexandra Eala</t>
+        </is>
+      </c>
+      <c r="AT36" s="24" t="inlineStr">
+        <is>
+          <t>Alexandra Eala</t>
+        </is>
+      </c>
+      <c r="AU36" s="24" t="inlineStr">
+        <is>
+          <t>Alexandra Eala</t>
+        </is>
+      </c>
+      <c r="AV36" s="24" t="n"/>
+      <c r="AW36" s="24" t="n"/>
+      <c r="AX36" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY36" s="24" t="n"/>
+      <c r="AZ36" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA36" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BB36" s="24" t="inlineStr">
+        <is>
+          <t>surface_blended_elo</t>
+        </is>
+      </c>
+      <c r="BC36" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD36" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BE36" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BF36" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG36" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BH36" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T23:31:36.249636Z</t>
+        </is>
+      </c>
+      <c r="BI36" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ36" s="25" t="n"/>
+      <c r="BK36" s="26" t="n">
+        <v>-117</v>
+      </c>
+      <c r="BL36" s="27" t="n">
+        <v>1.854701</v>
+      </c>
+      <c r="BM36" s="28" t="n">
+        <v>0.539171</v>
+      </c>
+      <c r="BN36" s="28" t="n"/>
+      <c r="BO36" s="28" t="n"/>
+      <c r="BP36" s="25" t="n"/>
+      <c r="BQ36" s="27" t="n">
+        <v>1.854701</v>
+      </c>
+      <c r="BR36" s="28" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="BS36" s="28" t="n"/>
+      <c r="BT36" s="28" t="n"/>
+      <c r="BU36" s="25" t="n"/>
+      <c r="BV36" s="29" t="n"/>
+      <c r="BW36" s="24" t="n"/>
+      <c r="BX36" s="30" t="n"/>
+      <c r="BY36" s="27" t="n"/>
+      <c r="BZ36" s="24" t="n"/>
+      <c r="CA36" s="31" t="n"/>
+      <c r="CB36" s="24" t="n"/>
+      <c r="CC36" s="24" t="n"/>
+      <c r="CD36" s="24" t="n"/>
+      <c r="CE36" s="24" t="n"/>
+      <c r="CF36" s="24" t="n"/>
+      <c r="CG36" s="24" t="n"/>
+      <c r="CH36" s="24" t="n"/>
+      <c r="CI36" s="24" t="n"/>
+      <c r="CJ36" s="24" t="n"/>
+      <c r="CK36" s="24" t="n"/>
+      <c r="CL36" s="24" t="n"/>
+      <c r="CM36" s="24" t="n"/>
+      <c r="CN36" s="24" t="n"/>
+      <c r="CO36" s="24" t="n"/>
+      <c r="CP36" s="24" t="n"/>
+      <c r="CQ36" s="24" t="n"/>
+      <c r="CR36" s="24" t="n"/>
+      <c r="CS36" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="36" customHeight="1">
+      <c r="A37" s="24" t="inlineStr">
+        <is>
+          <t>190d2b81db0c41d2</t>
+        </is>
+      </c>
+      <c r="B37" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-10T16:35:12.075143Z</t>
+        </is>
+      </c>
+      <c r="C37" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-11T00:30Z</t>
+        </is>
+      </c>
+      <c r="D37" s="24" t="inlineStr">
+        <is>
+          <t>421-2026:182217</t>
+        </is>
+      </c>
+      <c r="E37" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F37" s="24" t="inlineStr">
+        <is>
+          <t>Elina Svitolina</t>
+        </is>
+      </c>
+      <c r="G37" s="24" t="inlineStr">
+        <is>
+          <t>Ekaterina Alexandrova</t>
+        </is>
+      </c>
+      <c r="H37" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I37" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J37" s="25" t="n"/>
+      <c r="K37" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L37" s="26" t="n">
+        <v>-245</v>
+      </c>
+      <c r="M37" s="27" t="n">
+        <v>1.408163</v>
+      </c>
+      <c r="N37" s="28" t="n">
+        <v>0.710145</v>
+      </c>
+      <c r="O37" s="28" t="n">
+        <v>0.765165</v>
+      </c>
+      <c r="P37" s="28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q37" s="28" t="n">
+        <v>0.05502</v>
+      </c>
+      <c r="R37" s="26" t="n">
+        <v>48</v>
+      </c>
+      <c r="S37" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T37" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U37" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V37" s="24" t="n"/>
+      <c r="W37" s="26" t="n"/>
+      <c r="X37" s="26" t="n"/>
+      <c r="Y37" s="25" t="n"/>
+      <c r="Z37" s="26" t="n"/>
+      <c r="AA37" s="28" t="n"/>
+      <c r="AB37" s="28" t="n"/>
+      <c r="AC37" s="30" t="n"/>
+      <c r="AD37" s="24" t="n"/>
+      <c r="AE37" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo on Hard: Elina Svitolina p=0.765 vs Ekaterina Alexandrova. Executable ask 0.7100 (aec-wta-ekaale-elisvi-2026-08-11).</t>
+        </is>
+      </c>
+      <c r="AF37" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo model; singles only, WTA+ATP market coverage, not yet locked-holdout qualified -- promoted by explicit operator directive, not genuine walk-forward validation.</t>
+        </is>
+      </c>
+      <c r="AG37" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH37" s="24" t="n"/>
+      <c r="AI37" s="31" t="n"/>
+      <c r="AJ37" s="31" t="n"/>
+      <c r="AK37" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL37" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM37" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN37" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO37" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP37" s="24" t="inlineStr">
+        <is>
+          <t>Elina Svitolina</t>
+        </is>
+      </c>
+      <c r="AQ37" s="24" t="inlineStr">
+        <is>
+          <t>Elina Svitolina</t>
+        </is>
+      </c>
+      <c r="AR37" s="24" t="inlineStr">
+        <is>
+          <t>Elina Svitolina</t>
+        </is>
+      </c>
+      <c r="AS37" s="24" t="inlineStr">
+        <is>
+          <t>Ekaterina Alexandrova</t>
+        </is>
+      </c>
+      <c r="AT37" s="24" t="inlineStr">
+        <is>
+          <t>Ekaterina Alexandrova</t>
+        </is>
+      </c>
+      <c r="AU37" s="24" t="inlineStr">
+        <is>
+          <t>Ekaterina Alexandrova</t>
+        </is>
+      </c>
+      <c r="AV37" s="24" t="n"/>
+      <c r="AW37" s="24" t="n"/>
+      <c r="AX37" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY37" s="24" t="n"/>
+      <c r="AZ37" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA37" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BB37" s="24" t="inlineStr">
+        <is>
+          <t>surface_blended_elo</t>
+        </is>
+      </c>
+      <c r="BC37" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD37" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BE37" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BF37" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG37" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BH37" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-10T16:34:18.936432Z</t>
+        </is>
+      </c>
+      <c r="BI37" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ37" s="25" t="n"/>
+      <c r="BK37" s="26" t="n">
+        <v>-245</v>
+      </c>
+      <c r="BL37" s="27" t="n">
+        <v>1.408163</v>
+      </c>
+      <c r="BM37" s="28" t="n">
+        <v>0.710145</v>
+      </c>
+      <c r="BN37" s="28" t="n"/>
+      <c r="BO37" s="28" t="n"/>
+      <c r="BP37" s="25" t="n"/>
+      <c r="BQ37" s="27" t="n"/>
+      <c r="BR37" s="28" t="n"/>
+      <c r="BS37" s="28" t="n"/>
+      <c r="BT37" s="28" t="n"/>
+      <c r="BU37" s="25" t="n"/>
+      <c r="BV37" s="29" t="n"/>
+      <c r="BW37" s="24" t="n"/>
+      <c r="BX37" s="30" t="n"/>
+      <c r="BY37" s="27" t="n"/>
+      <c r="BZ37" s="24" t="n"/>
+      <c r="CA37" s="31" t="n"/>
+      <c r="CB37" s="24" t="n"/>
+      <c r="CC37" s="24" t="n"/>
+      <c r="CD37" s="24" t="n"/>
+      <c r="CE37" s="24" t="n"/>
+      <c r="CF37" s="24" t="n"/>
+      <c r="CG37" s="24" t="n"/>
+      <c r="CH37" s="24" t="n"/>
+      <c r="CI37" s="24" t="n"/>
+      <c r="CJ37" s="24" t="n"/>
+      <c r="CK37" s="24" t="n"/>
+      <c r="CL37" s="24" t="n"/>
+      <c r="CM37" s="24" t="n"/>
+      <c r="CN37" s="24" t="n"/>
+      <c r="CO37" s="24" t="n"/>
+      <c r="CP37" s="24" t="n"/>
+      <c r="CQ37" s="24" t="n"/>
+      <c r="CR37" s="24" t="n"/>
+      <c r="CS37" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="36" customHeight="1">
+      <c r="A38" s="24" t="inlineStr">
+        <is>
+          <t>bcfef55f34a1481a</t>
+        </is>
+      </c>
+      <c r="B38" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-10T16:35:12.075143Z</t>
+        </is>
+      </c>
+      <c r="C38" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-10T22:00Z</t>
+        </is>
+      </c>
+      <c r="D38" s="24" t="inlineStr">
+        <is>
+          <t>421-2026:181722</t>
+        </is>
+      </c>
+      <c r="E38" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F38" s="24" t="inlineStr">
+        <is>
+          <t>Arthur Fils</t>
+        </is>
+      </c>
+      <c r="G38" s="24" t="inlineStr">
+        <is>
+          <t>Rafael Jodar</t>
+        </is>
+      </c>
+      <c r="H38" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I38" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J38" s="25" t="n"/>
+      <c r="K38" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L38" s="26" t="n">
+        <v>117</v>
+      </c>
+      <c r="M38" s="27" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="N38" s="28" t="n">
+        <v>0.460829</v>
+      </c>
+      <c r="O38" s="28" t="n">
+        <v>0.609065</v>
+      </c>
+      <c r="P38" s="28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q38" s="28" t="n">
+        <v>0.148236</v>
+      </c>
+      <c r="R38" s="26" t="n">
+        <v>94</v>
+      </c>
+      <c r="S38" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T38" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U38" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V38" s="24" t="n"/>
+      <c r="W38" s="26" t="n"/>
+      <c r="X38" s="26" t="n"/>
+      <c r="Y38" s="25" t="n"/>
+      <c r="Z38" s="26" t="n"/>
+      <c r="AA38" s="28" t="n"/>
+      <c r="AB38" s="28" t="n"/>
+      <c r="AC38" s="30" t="n"/>
+      <c r="AD38" s="24" t="n"/>
+      <c r="AE38" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo on Hard: Arthur Fils p=0.609 vs Rafael Jodar. Executable ask 0.4600 (aec-atp-rafjod-artfil-2026-08-11).</t>
+        </is>
+      </c>
+      <c r="AF38" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo model; singles only, WTA+ATP market coverage, not yet locked-holdout qualified -- promoted by explicit operator directive, not genuine walk-forward validation.</t>
+        </is>
+      </c>
+      <c r="AG38" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH38" s="24" t="n"/>
+      <c r="AI38" s="31" t="n"/>
+      <c r="AJ38" s="31" t="n"/>
+      <c r="AK38" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL38" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM38" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN38" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO38" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP38" s="24" t="inlineStr">
+        <is>
+          <t>Arthur Fils</t>
+        </is>
+      </c>
+      <c r="AQ38" s="24" t="inlineStr">
+        <is>
+          <t>Arthur Fils</t>
+        </is>
+      </c>
+      <c r="AR38" s="24" t="inlineStr">
+        <is>
+          <t>Arthur Fils</t>
+        </is>
+      </c>
+      <c r="AS38" s="24" t="inlineStr">
+        <is>
+          <t>Rafael Jodar</t>
+        </is>
+      </c>
+      <c r="AT38" s="24" t="inlineStr">
+        <is>
+          <t>Rafael Jodar</t>
+        </is>
+      </c>
+      <c r="AU38" s="24" t="inlineStr">
+        <is>
+          <t>Rafael Jodar</t>
+        </is>
+      </c>
+      <c r="AV38" s="24" t="n"/>
+      <c r="AW38" s="24" t="n"/>
+      <c r="AX38" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY38" s="24" t="n"/>
+      <c r="AZ38" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA38" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BB38" s="24" t="inlineStr">
+        <is>
+          <t>surface_blended_elo</t>
+        </is>
+      </c>
+      <c r="BC38" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD38" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BE38" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BF38" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG38" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BH38" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-10T16:34:20.296833Z</t>
+        </is>
+      </c>
+      <c r="BI38" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ38" s="25" t="n"/>
+      <c r="BK38" s="26" t="n">
+        <v>117</v>
+      </c>
+      <c r="BL38" s="27" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BM38" s="28" t="n">
+        <v>0.460829</v>
+      </c>
+      <c r="BN38" s="28" t="n"/>
+      <c r="BO38" s="28" t="n"/>
+      <c r="BP38" s="25" t="n"/>
+      <c r="BQ38" s="27" t="n"/>
+      <c r="BR38" s="28" t="n"/>
+      <c r="BS38" s="28" t="n"/>
+      <c r="BT38" s="28" t="n"/>
+      <c r="BU38" s="25" t="n"/>
+      <c r="BV38" s="29" t="n"/>
+      <c r="BW38" s="24" t="n"/>
+      <c r="BX38" s="30" t="n"/>
+      <c r="BY38" s="27" t="n"/>
+      <c r="BZ38" s="24" t="n"/>
+      <c r="CA38" s="31" t="n"/>
+      <c r="CB38" s="24" t="n"/>
+      <c r="CC38" s="24" t="n"/>
+      <c r="CD38" s="24" t="n"/>
+      <c r="CE38" s="24" t="n"/>
+      <c r="CF38" s="24" t="n"/>
+      <c r="CG38" s="24" t="n"/>
+      <c r="CH38" s="24" t="n"/>
+      <c r="CI38" s="24" t="n"/>
+      <c r="CJ38" s="24" t="n"/>
+      <c r="CK38" s="24" t="n"/>
+      <c r="CL38" s="24" t="n"/>
+      <c r="CM38" s="24" t="n"/>
+      <c r="CN38" s="24" t="n"/>
+      <c r="CO38" s="24" t="n"/>
+      <c r="CP38" s="24" t="n"/>
+      <c r="CQ38" s="24" t="n"/>
+      <c r="CR38" s="24" t="n"/>
+      <c r="CS38" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
